--- a/Запрещённые_предметы_по_неделям_пример.xlsx
+++ b/Запрещённые_предметы_по_неделям_пример.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t xml:space="preserve">Неделя к неделе: последняя заполненная против предыдущей</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t xml:space="preserve">Всего попыток проноса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цвет конверсии по строке: зелёная неделя с наименьшей долей изъятий, красная с наибольшей.</t>
   </si>
   <si>
     <t xml:space="preserve">Месяц к месяцу: текущий против прошлого</t>
@@ -700,9 +697,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -726,39 +723,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$B$3:$B$10</c:f>
+              <c:f>Служебный!$B$3:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>96451</c:v>
+                  <c:v>97588</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>102495</c:v>
+                  <c:v>108106</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96686</c:v>
+                  <c:v>97150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>98975</c:v>
+                  <c:v>98051</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101080</c:v>
+                  <c:v>105018</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>107342</c:v>
+                  <c:v>100955</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>118920</c:v>
+                  <c:v>107393</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>112911</c:v>
+                  <c:v>116898</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>109740</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>106757</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>101131</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>103931</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>96072</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>113958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>111533</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95764</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>93118</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>99072</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>100312</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>108756</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>106103</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>104608</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>101748</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>98516</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>99299</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>110550</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -766,8 +871,8 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="68669814"/>
-        <c:axId val="32830877"/>
+        <c:axId val="4414320"/>
+        <c:axId val="30070481"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -843,9 +948,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -869,39 +974,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$C$3:$C$10</c:f>
+              <c:f>Служебный!$C$3:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>6.22077531596355E-005</c:v>
+                  <c:v>6.14829692175267E-005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.87828674569491E-005</c:v>
+                  <c:v>5.55010822711043E-005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.17137951720001E-005</c:v>
+                  <c:v>6.17601646937725E-005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0621369032584E-005</c:v>
+                  <c:v>5.09938705367615E-005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.95726157499011E-005</c:v>
+                  <c:v>5.71330629035023E-005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.4528143690261E-005</c:v>
+                  <c:v>5.94324203853202E-005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.88631012445341E-005</c:v>
+                  <c:v>6.51811570586537E-005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.0852264172667E-005</c:v>
+                  <c:v>5.13267977210902E-005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.46746856205577E-005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.62024035894602E-005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.94408242774224E-005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.81088414428804E-005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.20443001082521E-005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.14261394548869E-005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.27616938484574E-005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.22116870640324E-005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.44343735904981E-005</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.0655684754522E-005</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.97511763298509E-005</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.43642649600942E-005</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.59736293978493E-005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.73569899051698E-005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.89692180681684E-005</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.10544480084453E-005</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.04941640902728E-005</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.33197648123021E-005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -979,9 +1192,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -1005,39 +1218,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$D$3:$D$10</c:f>
+              <c:f>Служебный!$D$3:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.00300670806938238</c:v>
+                  <c:v>0.00440627946058942</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0027806234450461</c:v>
+                  <c:v>0.00407932954692617</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00372339325238401</c:v>
+                  <c:v>0.00374678332475553</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00400101035615054</c:v>
+                  <c:v>0.0035491733893586</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00455085081123862</c:v>
+                  <c:v>0.00331371764840313</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00400588772335153</c:v>
+                  <c:v>0.00410083700658709</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.00402791792801884</c:v>
+                  <c:v>0.00383637667259505</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0033566260151801</c:v>
+                  <c:v>0.00334479631815771</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.00328959358483689</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00374682690596401</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00354985118311893</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.00351194542533027</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00473603130985095</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00352761543726636</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00238494436624138</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.00388454951756401</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0043600592796237</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.00405765503875969</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.00504426190286307</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.00419287211740042</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.00368509844207987</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0031068369531967</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.00464874002437394</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.00423281497421739</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.00459219126073777</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.00454997738579828</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1115,9 +1436,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -1141,39 +1462,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$E$3:$E$10</c:f>
+              <c:f>Служебный!$E$3:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.00205285585426797</c:v>
+                  <c:v>0.00197770217649711</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00196107127176935</c:v>
+                  <c:v>0.00165578228775461</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0016755269635728</c:v>
+                  <c:v>0.00186309830159547</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00235412983076535</c:v>
+                  <c:v>0.00181538179110871</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00155322516818362</c:v>
+                  <c:v>0.00188539107581557</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00163030314322446</c:v>
+                  <c:v>0.00166410777078897</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0010427177934746</c:v>
+                  <c:v>0.00162021733260082</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.00106278396259</c:v>
+                  <c:v>0.0013259422744615</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.00132130490249681</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00165797090588908</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00165132353086591</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.00194359719429237</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00167582646348572</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00142157637024167</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00156904234621144</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.00137838853849046</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.00204042183036577</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.00189760981912145</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.00166480580588564</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.00120453124425319</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.00157394230134869</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.00167291220556745</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.00196564060227228</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.00208088026310447</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.00183284826634709</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.00144730890999548</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1251,9 +1680,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -1277,39 +1706,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$F$3:$F$10</c:f>
+              <c:f>Служебный!$F$3:$F$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.00124415506319271</c:v>
+                  <c:v>0.00102471615362545</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00122932825991512</c:v>
+                  <c:v>0.00107302092390802</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.001499700059988</c:v>
+                  <c:v>0.00101904271744725</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00137408436473857</c:v>
+                  <c:v>0.00155021366431755</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00118717847249703</c:v>
+                  <c:v>0.00150450398979223</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.000996813921857241</c:v>
+                  <c:v>0.00142637808924768</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000992263706693576</c:v>
+                  <c:v>0.000959094168148762</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.00146132794856126</c:v>
+                  <c:v>0.000684357302947869</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.000938582103152907</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00136759182067686</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00131512592577943</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.00150099585301787</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00100965942210009</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00119342213798066</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00126419983323321</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.00147236957520571</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0016430765265577</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.00150395671834625</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.000927107424834516</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.00120453124425319</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.00123464935015975</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.00146260324258183</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.00138577662460196</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.00164440293962402</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.00108762424596421</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.000931705110809588</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1387,9 +1924,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -1413,39 +1950,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$G$3:$G$10</c:f>
+              <c:f>Служебный!$G$3:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.03679588599392E-005</c:v>
+                  <c:v>1.02471615362545E-005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.75657349138982E-006</c:v>
+                  <c:v>9.25018037851738E-006</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.03427590344E-005</c:v>
+                  <c:v>1.02933607822954E-005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.01035615054307E-005</c:v>
+                  <c:v>1.01987741073523E-005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.97863078749505E-005</c:v>
+                  <c:v>1.90443543011674E-005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.79480538838479E-005</c:v>
+                  <c:v>9.90540339755337E-006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.40901446350488E-006</c:v>
+                  <c:v>9.31159386552196E-006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.77130660431667E-005</c:v>
+                  <c:v>8.55446628684836E-006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.82248952068526E-005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.36706726491003E-006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.88816485548447E-006</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.62176828857607E-006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.04088600216504E-005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.77516277926956E-006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.79319125281307E-005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.0884674825613E-005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.1478124530166E-005</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0093669250646E-005</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.96889704123136E-006</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.19489499429917E-006</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.88496083993855E-005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.91189966350566E-005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.8282030113614E-006</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.01506354297779E-005</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.0070594870039E-005</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.04568068747173E-006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1523,9 +2168,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Служебный!$A$3:$A$10</c:f>
+              <c:f>Служебный!$A$3:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>06.07</c:v>
                 </c:pt>
@@ -1549,39 +2194,147 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>24.08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>07.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.09</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02.11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>09.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23.11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>07.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Служебный!$H$3:$H$10</c:f>
+              <c:f>Служебный!$H$3:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.00637629469886264</c:v>
+                  <c:v>0.00748042792146575</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00602956241767891</c:v>
+                  <c:v>0.00687288402123841</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00696067683015121</c:v>
+                  <c:v>0.00670097786927432</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00779994948219247</c:v>
+                  <c:v>0.00697596148942897</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00735061337554412</c:v>
+                  <c:v>0.0067797901312156</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00673548098600734</c:v>
+                  <c:v>0.00726066069040662</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.00613017154389506</c:v>
+                  <c:v>0.00649018092426881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.00596930325654719</c:v>
+                  <c:v>0.00541497715957501</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.00562238017131402</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00683795910338432</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00657562962889717</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.00701426908237196</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00748397035556666</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00621281524772285</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00529888015206262</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.00680840399314983</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.00812947013466784</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.00753997093023256</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0077258952069543</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.00667549376586119</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.00657851333138554</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0063188283878862</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.00806895467232771</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.0080393032603841</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.00759322853200939</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.00700135685210312</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1596,11 +2349,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="50396839"/>
-        <c:axId val="31406123"/>
+        <c:axId val="43744837"/>
+        <c:axId val="85158320"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68669814"/>
+        <c:axId val="4414320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1633,7 +2386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32830877"/>
+        <c:crossAx val="30070481"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1641,7 +2394,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32830877"/>
+        <c:axId val="30070481"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1708,12 +2461,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68669814"/>
+        <c:crossAx val="4414320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="50396839"/>
+        <c:axId val="43744837"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1746,7 +2499,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31406123"/>
+        <c:crossAx val="85158320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1754,7 +2507,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31406123"/>
+        <c:axId val="85158320"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -1823,7 +2576,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50396839"/>
+        <c:crossAx val="43744837"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2327,12 +3080,12 @@
       </c>
       <c r="B2" s="2" t="str">
         <f aca="false">IF(Служебный!$K$2&lt;2,"-","Неделя "&amp;(Служебный!$K$2-1)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-1)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-1)),"00"))</f>
-        <v>Неделя 7: 17.08 - 23.08</v>
+        <v>Неделя 25: 21.12 - 27.12</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="str">
         <f aca="false">IF(Служебный!$K$2&lt;1,"-","Неделя "&amp;(Служебный!$K$2-0)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-0)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-0)),"00"))</f>
-        <v>Неделя 8: 24.08 - 30.08</v>
+        <v>Неделя 26: 28.12 - 03.01</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -2371,25 +3124,25 @@
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$2-1))</f>
-        <v>118920</v>
+        <v>99299</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$2))</f>
-        <v>112911</v>
+        <v>110550</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">IF(OR(B4="",D4=""),"-",D4-B4)</f>
-        <v>-6009</v>
+        <v>11251</v>
       </c>
       <c r="G4" s="7" t="n">
         <f aca="false">IF(OR(B4="",D4="",B4=0),"-",D4/B4-1)</f>
-        <v>-0.0505297679112008</v>
+        <v>0.113304262882808</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>9</v>
@@ -2405,27 +3158,27 @@
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">IF(OR(B5="",$B$4="",$B$4=0),"-",B5/$B$4)</f>
-        <v>5.88631012445341E-005</v>
+        <v>7.04941640902728E-005</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$2))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">IF(OR(D5="",$D$4="",$D$4=0),"-",D5/$D$4)</f>
-        <v>7.0852264172667E-005</v>
+        <v>6.33197648123021E-005</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(OR(B5="",D5=""),"-",D5-B5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13" t="n">
         <f aca="false">IF(OR(B5="",D5="",B5=0),"-",D5/B5-1)</f>
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="H5" s="14" t="n">
         <f aca="false">IF(OR(C5="-",E5="-"),"-",(E5-C5)*100)</f>
-        <v>0.00119891629281328</v>
+        <v>-0.00071743992779707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2434,31 +3187,31 @@
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$2-1))</f>
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="C6" s="15" t="n">
         <f aca="false">IF(OR(B6="",$B$4="",$B$4=0),"-",B6/$B$4)</f>
-        <v>0.00402791792801884</v>
+        <v>0.00459219126073777</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$2))</f>
-        <v>379</v>
+        <v>503</v>
       </c>
       <c r="E6" s="15" t="n">
         <f aca="false">IF(OR(D6="",$D$4="",$D$4=0),"-",D6/$D$4)</f>
-        <v>0.0033566260151801</v>
+        <v>0.00454997738579828</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(OR(B6="",D6=""),"-",D6-B6)</f>
-        <v>-100</v>
+        <v>47</v>
       </c>
       <c r="G6" s="13" t="n">
         <f aca="false">IF(OR(B6="",D6="",B6=0),"-",D6/B6-1)</f>
-        <v>-0.208768267223382</v>
+        <v>0.103070175438597</v>
       </c>
       <c r="H6" s="16" t="n">
         <f aca="false">IF(OR(C6="-",E6="-"),"-",(E6-C6)*100)</f>
-        <v>-0.0671291912838738</v>
+        <v>-0.00422138749394899</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2467,31 +3220,31 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$2-1))</f>
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="C7" s="15" t="n">
         <f aca="false">IF(OR(B7="",$B$4="",$B$4=0),"-",B7/$B$4)</f>
-        <v>0.0010427177934746</v>
+        <v>0.00183284826634709</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$2))</f>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="E7" s="15" t="n">
         <f aca="false">IF(OR(D7="",$D$4="",$D$4=0),"-",D7/$D$4)</f>
-        <v>0.00106278396259</v>
+        <v>0.00144730890999548</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(OR(B7="",D7=""),"-",D7-B7)</f>
-        <v>-4</v>
+        <v>-22</v>
       </c>
       <c r="G7" s="13" t="n">
         <f aca="false">IF(OR(B7="",D7="",B7=0),"-",D7/B7-1)</f>
-        <v>-0.032258064516129</v>
+        <v>-0.120879120879121</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">IF(OR(C7="-",E7="-"),"-",(E7-C7)*100)</f>
-        <v>0.00200661691153999</v>
+        <v>-0.0385539356351616</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2500,31 +3253,31 @@
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$2-1))</f>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">IF(OR(B8="",$B$4="",$B$4=0),"-",B8/$B$4)</f>
-        <v>0.000992263706693576</v>
+        <v>0.00108762424596421</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$2))</f>
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">IF(OR(D8="",$D$4="",$D$4=0),"-",D8/$D$4)</f>
-        <v>0.00146132794856126</v>
+        <v>0.000931705110809588</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(OR(B8="",D8=""),"-",D8-B8)</f>
-        <v>47</v>
+        <v>-5</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">IF(OR(B8="",D8="",B8=0),"-",D8/B8-1)</f>
-        <v>0.398305084745763</v>
+        <v>-0.0462962962962963</v>
       </c>
       <c r="H8" s="16" t="n">
         <f aca="false">IF(OR(C8="-",E8="-"),"-",(E8-C8)*100)</f>
-        <v>0.0469064241867681</v>
+        <v>-0.0155919135154621</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2537,27 +3290,27 @@
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">IF(OR(B9="",$B$4="",$B$4=0),"-",B9/$B$4)</f>
-        <v>8.40901446350488E-006</v>
+        <v>1.0070594870039E-005</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$2))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IF(OR(D9="",$D$4="",$D$4=0),"-",D9/$D$4)</f>
-        <v>1.77130660431667E-005</v>
+        <v>9.04568068747173E-006</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(OR(B9="",D9=""),"-",D9-B9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
         <f aca="false">IF(OR(B9="",D9="",B9=0),"-",D9/B9-1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14" t="n">
         <f aca="false">IF(OR(C9="-",E9="-"),"-",(E9-C9)*100)</f>
-        <v>0.000930405157966187</v>
+        <v>-0.000102491418256724</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2566,37 +3319,37 @@
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$2-1))</f>
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">IF(OR(B10="",$B$4="",$B$4=0),"-",B10/$B$4)</f>
-        <v>0.00613017154389506</v>
+        <v>0.00759322853200939</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$2))</f>
-        <v>674</v>
+        <v>774</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">IF(OR(D10="",$D$4="",$D$4=0),"-",D10/$D$4)</f>
-        <v>0.00596930325654719</v>
+        <v>0.00700135685210312</v>
       </c>
       <c r="F10" s="20" t="n">
         <f aca="false">IF(OR(B10="",D10=""),"-",D10-B10)</f>
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="G10" s="21" t="n">
         <f aca="false">IF(OR(B10="",D10="",B10=0),"-",D10/B10-1)</f>
-        <v>-0.0754458161865569</v>
+        <v>0.0265251989389921</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">IF(OR(C10="-",E10="-"),"-",(E10-C10)*100)</f>
-        <v>-0.0160868287347863</v>
+        <v>-0.0591871679906265</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="str">
         <f aca="false">IF(Служебный!$K$3="","Недели текущего месяца","Недели текущего месяца: "&amp;CHOOSE(MONTH(Служебный!$K$3),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$3))</f>
-        <v>Недели текущего месяца: Август 2026</v>
+        <v>Недели текущего месяца: Декабрь 2026</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2605,27 +3358,27 @@
       </c>
       <c r="B13" s="2" t="str">
         <f aca="false">IF(Служебный!$K$7="","Неделя 1","Неделя 1: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$7)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$7)),"00"))</f>
-        <v>Неделя 1: 03.08 - 09.08</v>
+        <v>Неделя 1: 07.12 - 13.12</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="str">
         <f aca="false">IF(Служебный!$K$8="","Неделя 2","Неделя 2: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$8)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$8)),"00"))</f>
-        <v>Неделя 2: 10.08 - 16.08</v>
+        <v>Неделя 2: 14.12 - 20.12</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="str">
         <f aca="false">IF(Служебный!$K$9="","Неделя 3","Неделя 3: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$9)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$9)),"00"))</f>
-        <v>Неделя 3: 17.08 - 23.08</v>
+        <v>Неделя 3: 21.12 - 27.12</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="str">
         <f aca="false">IF(Служебный!$K$10="","Неделя 4","Неделя 4: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$10)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$10)),"00"))</f>
-        <v>Неделя 4: 24.08 - 30.08</v>
+        <v>Неделя 4: 28.12 - 03.01</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="str">
         <f aca="false">IF(Служебный!$K$11="","Неделя 5","Неделя 5: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$11)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$11)),"00"))</f>
-        <v>Неделя 5: 31.08 - 06.09</v>
+        <v>Неделя 5</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -2668,28 +3421,28 @@
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)))</f>
-        <v>101080</v>
+        <v>101748</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="4" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)))</f>
-        <v>107342</v>
+        <v>98516</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)))</f>
-        <v>118920</v>
+        <v>99299</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="4" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)))</f>
-        <v>112911</v>
+        <v>110550</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>9</v>
@@ -2708,19 +3461,19 @@
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$7)))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="23" t="n">
         <f aca="false">IF(OR(B16="",B$15="",B$15=0),"",B16/B$15)</f>
-        <v>3.95726157499011E-005</v>
+        <v>5.89692180681684E-005</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$8)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">IF(OR(D16="",D$15="",D$15=0),"",D16/D$15)</f>
-        <v>7.4528143690261E-005</v>
+        <v>7.10544480084453E-005</v>
       </c>
       <c r="F16" s="10" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$9)))</f>
@@ -2728,15 +3481,15 @@
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">IF(OR(F16="",F$15="",F$15=0),"",F16/F$15)</f>
-        <v>5.88631012445341E-005</v>
+        <v>7.04941640902728E-005</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$10)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" s="23" t="n">
         <f aca="false">IF(OR(H16="",H$15="",H$15=0),"",H16/H$15)</f>
-        <v>7.0852264172667E-005</v>
+        <v>6.33197648123021E-005</v>
       </c>
       <c r="J16" s="10" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$11)))</f>
@@ -2753,35 +3506,35 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$7)))</f>
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">IF(OR(B17="",B$15="",B$15=0),"",B17/B$15)</f>
-        <v>0.00455085081123862</v>
+        <v>0.00464874002437394</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$8)))</f>
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="E17" s="24" t="n">
         <f aca="false">IF(OR(D17="",D$15="",D$15=0),"",D17/D$15)</f>
-        <v>0.00400588772335153</v>
+        <v>0.00423281497421739</v>
       </c>
       <c r="F17" s="10" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$9)))</f>
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="G17" s="24" t="n">
         <f aca="false">IF(OR(F17="",F$15="",F$15=0),"",F17/F$15)</f>
-        <v>0.00402791792801884</v>
+        <v>0.00459219126073777</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$10)))</f>
-        <v>379</v>
+        <v>503</v>
       </c>
       <c r="I17" s="24" t="n">
         <f aca="false">IF(OR(H17="",H$15="",H$15=0),"",H17/H$15)</f>
-        <v>0.0033566260151801</v>
+        <v>0.00454997738579828</v>
       </c>
       <c r="J17" s="10" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$11)))</f>
@@ -2798,35 +3551,35 @@
       </c>
       <c r="B18" s="10" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$7)))</f>
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="C18" s="24" t="n">
         <f aca="false">IF(OR(B18="",B$15="",B$15=0),"",B18/B$15)</f>
-        <v>0.00155322516818362</v>
+        <v>0.00196564060227228</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$8)))</f>
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E18" s="24" t="n">
         <f aca="false">IF(OR(D18="",D$15="",D$15=0),"",D18/D$15)</f>
-        <v>0.00163030314322446</v>
+        <v>0.00208088026310447</v>
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$9)))</f>
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="G18" s="24" t="n">
         <f aca="false">IF(OR(F18="",F$15="",F$15=0),"",F18/F$15)</f>
-        <v>0.0010427177934746</v>
+        <v>0.00183284826634709</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$10)))</f>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="I18" s="24" t="n">
         <f aca="false">IF(OR(H18="",H$15="",H$15=0),"",H18/H$15)</f>
-        <v>0.00106278396259</v>
+        <v>0.00144730890999548</v>
       </c>
       <c r="J18" s="10" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$11)))</f>
@@ -2843,35 +3596,35 @@
       </c>
       <c r="B19" s="10" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$7)))</f>
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">IF(OR(B19="",B$15="",B$15=0),"",B19/B$15)</f>
-        <v>0.00118717847249703</v>
+        <v>0.00138577662460196</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$8)))</f>
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="E19" s="24" t="n">
         <f aca="false">IF(OR(D19="",D$15="",D$15=0),"",D19/D$15)</f>
-        <v>0.000996813921857241</v>
+        <v>0.00164440293962402</v>
       </c>
       <c r="F19" s="10" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$9)))</f>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G19" s="24" t="n">
         <f aca="false">IF(OR(F19="",F$15="",F$15=0),"",F19/F$15)</f>
-        <v>0.000992263706693576</v>
+        <v>0.00108762424596421</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$10)))</f>
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="I19" s="24" t="n">
         <f aca="false">IF(OR(H19="",H$15="",H$15=0),"",H19/H$15)</f>
-        <v>0.00146132794856126</v>
+        <v>0.000931705110809588</v>
       </c>
       <c r="J19" s="10" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$11)))</f>
@@ -2888,19 +3641,19 @@
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$7)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="23" t="n">
         <f aca="false">IF(OR(B20="",B$15="",B$15=0),"",B20/B$15)</f>
-        <v>1.97863078749505E-005</v>
+        <v>9.8282030113614E-006</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$8)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">IF(OR(D20="",D$15="",D$15=0),"",D20/D$15)</f>
-        <v>2.79480538838479E-005</v>
+        <v>1.01506354297779E-005</v>
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$9)))</f>
@@ -2908,15 +3661,15 @@
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">IF(OR(F20="",F$15="",F$15=0),"",F20/F$15)</f>
-        <v>8.40901446350488E-006</v>
+        <v>1.0070594870039E-005</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$10)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="23" t="n">
         <f aca="false">IF(OR(H20="",H$15="",H$15=0),"",H20/H$15)</f>
-        <v>1.77130660431667E-005</v>
+        <v>9.04568068747173E-006</v>
       </c>
       <c r="J20" s="10" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$11)))</f>
@@ -2933,35 +3686,35 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$7)))</f>
-        <v>743</v>
+        <v>821</v>
       </c>
       <c r="C21" s="25" t="n">
         <f aca="false">IF(OR(B21="",B$15="",B$15=0),"",B21/B$15)</f>
-        <v>0.00735061337554412</v>
+        <v>0.00806895467232771</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$8)))</f>
-        <v>723</v>
+        <v>792</v>
       </c>
       <c r="E21" s="25" t="n">
         <f aca="false">IF(OR(D21="",D$15="",D$15=0),"",D21/D$15)</f>
-        <v>0.00673548098600734</v>
+        <v>0.0080393032603841</v>
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$9)))</f>
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF(OR(F21="",F$15="",F$15=0),"",F21/F$15)</f>
-        <v>0.00613017154389506</v>
+        <v>0.00759322853200939</v>
       </c>
       <c r="H21" s="18" t="n">
         <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$10)))</f>
-        <v>674</v>
+        <v>774</v>
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">IF(OR(H21="",H$15="",H$15=0),"",H21/H$15)</f>
-        <v>0.00596930325654719</v>
+        <v>0.00700135685210312</v>
       </c>
       <c r="J21" s="18" t="str">
         <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$11)))</f>
@@ -2972,14 +3725,9 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>16</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2988,12 +3736,12 @@
       </c>
       <c r="B25" s="2" t="str">
         <f aca="false">IF(Служебный!$K$4="","-",CHOOSE(MONTH(Служебный!$K$4),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$4)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")&amp;")")</f>
-        <v>Июль 2026 (недель: 4)</v>
+        <v>Ноябрь 2026 (недель: 5)</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="str">
         <f aca="false">IF(Служебный!$K$3="","-",CHOOSE(MONTH(Служебный!$K$3),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$3)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")&amp;")")</f>
-        <v>Август 2026 (недель: 4)</v>
+        <v>Декабрь 2026 (недель: 4)</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
@@ -3032,25 +3780,25 @@
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$80:$D$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>394607</v>
+        <v>518851</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="4" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$80:$D$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>440253</v>
+        <v>410113</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="6" t="n">
         <f aca="false">IF(OR(B27="",D27=""),"-",D27-B27)</f>
-        <v>45646</v>
+        <v>-108738</v>
       </c>
       <c r="G27" s="7" t="n">
         <f aca="false">IF(OR(B27="",D27="",B27=0),"-",D27/B27-1)</f>
-        <v>0.115674582559357</v>
+        <v>-0.209574617761168</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>9</v>
@@ -3062,11 +3810,11 @@
       </c>
       <c r="B28" s="10" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$80:$E$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C28" s="11" t="n">
         <f aca="false">IF(OR(B28="",$B$27="",$B$27=0),"-",B28/$B$27)</f>
-        <v>5.57516719166158E-005</v>
+        <v>6.74567457709439E-005</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$80:$E$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
@@ -3074,19 +3822,19 @@
       </c>
       <c r="E28" s="11" t="n">
         <f aca="false">IF(OR(D28="",$D$27="",$D$27=0),"-",D28/$D$27)</f>
-        <v>6.13283725494205E-005</v>
+        <v>6.58355136267321E-005</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">IF(OR(B28="",D28=""),"-",D28-B28)</f>
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G28" s="13" t="n">
         <f aca="false">IF(OR(B28="",D28="",B28=0),"-",D28/B28-1)</f>
-        <v>0.227272727272727</v>
+        <v>-0.228571428571429</v>
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">IF(OR(C28="-",E28="-"),"-",(E28-C28)*100)</f>
-        <v>0.000557670063280468</v>
+        <v>-0.000162123214421174</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3095,31 +3843,31 @@
       </c>
       <c r="B29" s="10" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$80:$F$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>1331</v>
+        <v>2080</v>
       </c>
       <c r="C29" s="15" t="n">
         <f aca="false">IF(OR(B29="",$B$27="",$B$27=0),"-",B29/$B$27)</f>
-        <v>0.00337297615095525</v>
+        <v>0.00400885803438752</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$80:$F$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>1748</v>
+        <v>1849</v>
       </c>
       <c r="E29" s="15" t="n">
         <f aca="false">IF(OR(D29="",$D$27="",$D$27=0),"-",D29/$D$27)</f>
-        <v>0.00397044426727359</v>
+        <v>0.00450851350725288</v>
       </c>
       <c r="F29" s="12" t="n">
         <f aca="false">IF(OR(B29="",D29=""),"-",D29-B29)</f>
-        <v>417</v>
+        <v>-231</v>
       </c>
       <c r="G29" s="13" t="n">
         <f aca="false">IF(OR(B29="",D29="",B29=0),"-",D29/B29-1)</f>
-        <v>0.313298271975958</v>
+        <v>-0.111057692307692</v>
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">IF(OR(C29="-",E29="-"),"-",(E29-C29)*100)</f>
-        <v>0.0597468116318336</v>
+        <v>0.0499655472865357</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3128,31 +3876,31 @@
       </c>
       <c r="B30" s="10" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$80:$G$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">IF(OR(B30="",$B$27="",$B$27=0),"-",B30/$B$27)</f>
-        <v>0.00201212852280877</v>
+        <v>0.00159583387138119</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$80:$G$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>576</v>
+        <v>747</v>
       </c>
       <c r="E30" s="15" t="n">
         <f aca="false">IF(OR(D30="",$D$27="",$D$27=0),"-",D30/$D$27)</f>
-        <v>0.00130833861438764</v>
+        <v>0.00182144921033959</v>
       </c>
       <c r="F30" s="12" t="n">
         <f aca="false">IF(OR(B30="",D30=""),"-",D30-B30)</f>
-        <v>-218</v>
+        <v>-81</v>
       </c>
       <c r="G30" s="13" t="n">
         <f aca="false">IF(OR(B30="",D30="",B30=0),"-",D30/B30-1)</f>
-        <v>-0.27455919395466</v>
+        <v>-0.0978260869565217</v>
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">IF(OR(C30="-",E30="-"),"-",(E30-C30)*100)</f>
-        <v>-0.0703789908421133</v>
+        <v>0.0225615338958403</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3161,31 +3909,31 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$80:$H$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>527</v>
+        <v>657</v>
       </c>
       <c r="C31" s="15" t="n">
         <f aca="false">IF(OR(B31="",$B$27="",$B$27=0),"-",B31/$B$27)</f>
-        <v>0.00133550595909348</v>
+        <v>0.00126625948490029</v>
       </c>
       <c r="D31" s="10" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$80:$H$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E31" s="15" t="n">
         <f aca="false">IF(OR(D31="",$D$27="",$D$27=0),"-",D31/$D$27)</f>
-        <v>0.00115842481482239</v>
+        <v>0.00125331311126446</v>
       </c>
       <c r="F31" s="12" t="n">
         <f aca="false">IF(OR(B31="",D31=""),"-",D31-B31)</f>
-        <v>-17</v>
+        <v>-143</v>
       </c>
       <c r="G31" s="13" t="n">
         <f aca="false">IF(OR(B31="",D31="",B31=0),"-",D31/B31-1)</f>
-        <v>-0.032258064516129</v>
+        <v>-0.21765601217656</v>
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">IF(OR(C31="-",E31="-"),"-",(E31-C31)*100)</f>
-        <v>-0.0177081144271092</v>
+        <v>-0.00129463736358328</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3194,31 +3942,31 @@
       </c>
       <c r="B32" s="10" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$80:$I$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">IF(OR(B32="",$B$27="",$B$27=0),"-",B32/$B$27)</f>
-        <v>1.01366676212029E-005</v>
+        <v>1.34913491541888E-005</v>
       </c>
       <c r="D32" s="10" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$80:$I$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E32" s="11" t="n">
         <f aca="false">IF(OR(D32="",$D$27="",$D$27=0),"-",D32/$D$27)</f>
-        <v>1.81713696442727E-005</v>
+        <v>9.75340942618254E-006</v>
       </c>
       <c r="F32" s="12" t="n">
         <f aca="false">IF(OR(B32="",D32=""),"-",D32-B32)</f>
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G32" s="13" t="n">
         <f aca="false">IF(OR(B32="",D32="",B32=0),"-",D32/B32-1)</f>
-        <v>1</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">IF(OR(C32="-",E32="-"),"-",(E32-C32)*100)</f>
-        <v>0.000803470202306986</v>
+        <v>-0.000373793972800623</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3227,55 +3975,55 @@
       </c>
       <c r="B33" s="18" t="n">
         <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$80:$J$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
-        <v>2678</v>
+        <v>3607</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">IF(OR(B33="",$B$27="",$B$27=0),"-",B33/$B$27)</f>
-        <v>0.00678649897239532</v>
+        <v>0.00695189948559413</v>
       </c>
       <c r="D33" s="18" t="n">
         <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$80:$J$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
-        <v>2869</v>
+        <v>3141</v>
       </c>
       <c r="E33" s="19" t="n">
         <f aca="false">IF(OR(D33="",$D$27="",$D$27=0),"-",D33/$D$27)</f>
-        <v>0.00651670743867731</v>
+        <v>0.00765886475190984</v>
       </c>
       <c r="F33" s="20" t="n">
         <f aca="false">IF(OR(B33="",D33=""),"-",D33-B33)</f>
-        <v>191</v>
+        <v>-466</v>
       </c>
       <c r="G33" s="21" t="n">
         <f aca="false">IF(OR(B33="",D33="",B33=0),"-",D33/B33-1)</f>
-        <v>0.0713218820014936</v>
+        <v>-0.129193235375658</v>
       </c>
       <c r="H33" s="22" t="n">
         <f aca="false">IF(OR(C33="-",E33="-"),"-",(E33-C33)*100)</f>
-        <v>-0.0269791533718014</v>
+        <v>0.0706965266315709</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>10</v>
@@ -3296,22 +4044,22 @@
         <v>15</v>
       </c>
       <c r="K79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="N79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N79" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O79" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="P79" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3326,50 +4074,50 @@
         <v>46215</v>
       </c>
       <c r="D80" s="30" t="n">
-        <v>96451</v>
+        <v>97588</v>
       </c>
       <c r="E80" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F80" s="30" t="n">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="G80" s="30" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H80" s="30" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I80" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="10" t="n">
         <f aca="false">IF(COUNT(E80:I80)=0,"",SUM(E80:I80))</f>
-        <v>615</v>
+        <v>730</v>
       </c>
       <c r="K80" s="23" t="n">
         <f aca="false">IF(OR(D80="",E80="",D80=0),"",E80/D80)</f>
-        <v>6.22077531596355E-005</v>
+        <v>6.14829692175267E-005</v>
       </c>
       <c r="L80" s="24" t="n">
         <f aca="false">IF(OR(D80="",F80="",D80=0),"",F80/D80)</f>
-        <v>0.00300670806938238</v>
+        <v>0.00440627946058942</v>
       </c>
       <c r="M80" s="24" t="n">
         <f aca="false">IF(OR(D80="",G80="",D80=0),"",G80/D80)</f>
-        <v>0.00205285585426797</v>
+        <v>0.00197770217649711</v>
       </c>
       <c r="N80" s="24" t="n">
         <f aca="false">IF(OR(D80="",H80="",D80=0),"",H80/D80)</f>
-        <v>0.00124415506319271</v>
+        <v>0.00102471615362545</v>
       </c>
       <c r="O80" s="23" t="n">
         <f aca="false">IF(OR(D80="",I80="",D80=0),"",I80/D80)</f>
-        <v>1.03679588599392E-005</v>
+        <v>1.02471615362545E-005</v>
       </c>
       <c r="P80" s="24" t="n">
         <f aca="false">IF(OR(D80="",J80="",D80=0),"",J80/D80)</f>
-        <v>0.00637629469886264</v>
+        <v>0.00748042792146575</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3385,50 +4133,50 @@
         <v>46222</v>
       </c>
       <c r="D81" s="30" t="n">
-        <v>102495</v>
+        <v>108106</v>
       </c>
       <c r="E81" s="30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F81" s="30" t="n">
-        <v>285</v>
+        <v>441</v>
       </c>
       <c r="G81" s="30" t="n">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="H81" s="30" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I81" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="10" t="n">
         <f aca="false">IF(COUNT(E81:I81)=0,"",SUM(E81:I81))</f>
-        <v>618</v>
+        <v>743</v>
       </c>
       <c r="K81" s="23" t="n">
         <f aca="false">IF(OR(D81="",E81="",D81=0),"",E81/D81)</f>
-        <v>4.87828674569491E-005</v>
+        <v>5.55010822711043E-005</v>
       </c>
       <c r="L81" s="24" t="n">
         <f aca="false">IF(OR(D81="",F81="",D81=0),"",F81/D81)</f>
-        <v>0.0027806234450461</v>
+        <v>0.00407932954692617</v>
       </c>
       <c r="M81" s="24" t="n">
         <f aca="false">IF(OR(D81="",G81="",D81=0),"",G81/D81)</f>
-        <v>0.00196107127176935</v>
+        <v>0.00165578228775461</v>
       </c>
       <c r="N81" s="24" t="n">
         <f aca="false">IF(OR(D81="",H81="",D81=0),"",H81/D81)</f>
-        <v>0.00122932825991512</v>
+        <v>0.00107302092390802</v>
       </c>
       <c r="O81" s="23" t="n">
         <f aca="false">IF(OR(D81="",I81="",D81=0),"",I81/D81)</f>
-        <v>9.75657349138982E-006</v>
+        <v>9.25018037851738E-006</v>
       </c>
       <c r="P81" s="24" t="n">
         <f aca="false">IF(OR(D81="",J81="",D81=0),"",J81/D81)</f>
-        <v>0.00602956241767891</v>
+        <v>0.00687288402123841</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,50 +4192,50 @@
         <v>46229</v>
       </c>
       <c r="D82" s="30" t="n">
-        <v>96686</v>
+        <v>97150</v>
       </c>
       <c r="E82" s="30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" s="30" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="H82" s="30" t="n">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="I82" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="10" t="n">
         <f aca="false">IF(COUNT(E82:I82)=0,"",SUM(E82:I82))</f>
-        <v>673</v>
+        <v>651</v>
       </c>
       <c r="K82" s="23" t="n">
         <f aca="false">IF(OR(D82="",E82="",D82=0),"",E82/D82)</f>
-        <v>5.17137951720001E-005</v>
+        <v>6.17601646937725E-005</v>
       </c>
       <c r="L82" s="24" t="n">
         <f aca="false">IF(OR(D82="",F82="",D82=0),"",F82/D82)</f>
-        <v>0.00372339325238401</v>
+        <v>0.00374678332475553</v>
       </c>
       <c r="M82" s="24" t="n">
         <f aca="false">IF(OR(D82="",G82="",D82=0),"",G82/D82)</f>
-        <v>0.0016755269635728</v>
+        <v>0.00186309830159547</v>
       </c>
       <c r="N82" s="24" t="n">
         <f aca="false">IF(OR(D82="",H82="",D82=0),"",H82/D82)</f>
-        <v>0.001499700059988</v>
+        <v>0.00101904271744725</v>
       </c>
       <c r="O82" s="23" t="n">
         <f aca="false">IF(OR(D82="",I82="",D82=0),"",I82/D82)</f>
-        <v>1.03427590344E-005</v>
+        <v>1.02933607822954E-005</v>
       </c>
       <c r="P82" s="24" t="n">
         <f aca="false">IF(OR(D82="",J82="",D82=0),"",J82/D82)</f>
-        <v>0.00696067683015121</v>
+        <v>0.00670097786927432</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3503,50 +4251,50 @@
         <v>46236</v>
       </c>
       <c r="D83" s="30" t="n">
-        <v>98975</v>
+        <v>98051</v>
       </c>
       <c r="E83" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F83" s="30" t="n">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="G83" s="30" t="n">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="H83" s="30" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="I83" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="10" t="n">
         <f aca="false">IF(COUNT(E83:I83)=0,"",SUM(E83:I83))</f>
-        <v>772</v>
+        <v>684</v>
       </c>
       <c r="K83" s="23" t="n">
         <f aca="false">IF(OR(D83="",E83="",D83=0),"",E83/D83)</f>
-        <v>6.0621369032584E-005</v>
+        <v>5.09938705367615E-005</v>
       </c>
       <c r="L83" s="24" t="n">
         <f aca="false">IF(OR(D83="",F83="",D83=0),"",F83/D83)</f>
-        <v>0.00400101035615054</v>
+        <v>0.0035491733893586</v>
       </c>
       <c r="M83" s="24" t="n">
         <f aca="false">IF(OR(D83="",G83="",D83=0),"",G83/D83)</f>
-        <v>0.00235412983076535</v>
+        <v>0.00181538179110871</v>
       </c>
       <c r="N83" s="24" t="n">
         <f aca="false">IF(OR(D83="",H83="",D83=0),"",H83/D83)</f>
-        <v>0.00137408436473857</v>
+        <v>0.00155021366431755</v>
       </c>
       <c r="O83" s="23" t="n">
         <f aca="false">IF(OR(D83="",I83="",D83=0),"",I83/D83)</f>
-        <v>1.01035615054307E-005</v>
+        <v>1.01987741073523E-005</v>
       </c>
       <c r="P83" s="24" t="n">
         <f aca="false">IF(OR(D83="",J83="",D83=0),"",J83/D83)</f>
-        <v>0.00779994948219247</v>
+        <v>0.00697596148942897</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3562,50 +4310,50 @@
         <v>46243</v>
       </c>
       <c r="D84" s="30" t="n">
-        <v>101080</v>
+        <v>105018</v>
       </c>
       <c r="E84" s="30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F84" s="30" t="n">
-        <v>460</v>
+        <v>348</v>
       </c>
       <c r="G84" s="30" t="n">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="H84" s="30" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="I84" s="30" t="n">
         <v>2</v>
       </c>
       <c r="J84" s="10" t="n">
         <f aca="false">IF(COUNT(E84:I84)=0,"",SUM(E84:I84))</f>
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="K84" s="23" t="n">
         <f aca="false">IF(OR(D84="",E84="",D84=0),"",E84/D84)</f>
-        <v>3.95726157499011E-005</v>
+        <v>5.71330629035023E-005</v>
       </c>
       <c r="L84" s="24" t="n">
         <f aca="false">IF(OR(D84="",F84="",D84=0),"",F84/D84)</f>
-        <v>0.00455085081123862</v>
+        <v>0.00331371764840313</v>
       </c>
       <c r="M84" s="24" t="n">
         <f aca="false">IF(OR(D84="",G84="",D84=0),"",G84/D84)</f>
-        <v>0.00155322516818362</v>
+        <v>0.00188539107581557</v>
       </c>
       <c r="N84" s="24" t="n">
         <f aca="false">IF(OR(D84="",H84="",D84=0),"",H84/D84)</f>
-        <v>0.00118717847249703</v>
+        <v>0.00150450398979223</v>
       </c>
       <c r="O84" s="23" t="n">
         <f aca="false">IF(OR(D84="",I84="",D84=0),"",I84/D84)</f>
-        <v>1.97863078749505E-005</v>
+        <v>1.90443543011674E-005</v>
       </c>
       <c r="P84" s="24" t="n">
         <f aca="false">IF(OR(D84="",J84="",D84=0),"",J84/D84)</f>
-        <v>0.00735061337554412</v>
+        <v>0.0067797901312156</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3621,50 +4369,50 @@
         <v>46250</v>
       </c>
       <c r="D85" s="30" t="n">
-        <v>107342</v>
+        <v>100955</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F85" s="30" t="n">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H85" s="30" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="I85" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J85" s="10" t="n">
         <f aca="false">IF(COUNT(E85:I85)=0,"",SUM(E85:I85))</f>
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="K85" s="23" t="n">
         <f aca="false">IF(OR(D85="",E85="",D85=0),"",E85/D85)</f>
-        <v>7.4528143690261E-005</v>
+        <v>5.94324203853202E-005</v>
       </c>
       <c r="L85" s="24" t="n">
         <f aca="false">IF(OR(D85="",F85="",D85=0),"",F85/D85)</f>
-        <v>0.00400588772335153</v>
+        <v>0.00410083700658709</v>
       </c>
       <c r="M85" s="24" t="n">
         <f aca="false">IF(OR(D85="",G85="",D85=0),"",G85/D85)</f>
-        <v>0.00163030314322446</v>
+        <v>0.00166410777078897</v>
       </c>
       <c r="N85" s="24" t="n">
         <f aca="false">IF(OR(D85="",H85="",D85=0),"",H85/D85)</f>
-        <v>0.000996813921857241</v>
+        <v>0.00142637808924768</v>
       </c>
       <c r="O85" s="23" t="n">
         <f aca="false">IF(OR(D85="",I85="",D85=0),"",I85/D85)</f>
-        <v>2.79480538838479E-005</v>
+        <v>9.90540339755337E-006</v>
       </c>
       <c r="P85" s="24" t="n">
         <f aca="false">IF(OR(D85="",J85="",D85=0),"",J85/D85)</f>
-        <v>0.00673548098600734</v>
+        <v>0.00726066069040662</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3680,50 +4428,50 @@
         <v>46257</v>
       </c>
       <c r="D86" s="30" t="n">
-        <v>118920</v>
+        <v>107393</v>
       </c>
       <c r="E86" s="30" t="n">
         <v>7</v>
       </c>
       <c r="F86" s="30" t="n">
-        <v>479</v>
+        <v>412</v>
       </c>
       <c r="G86" s="30" t="n">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="H86" s="30" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="I86" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J86" s="10" t="n">
         <f aca="false">IF(COUNT(E86:I86)=0,"",SUM(E86:I86))</f>
-        <v>729</v>
+        <v>697</v>
       </c>
       <c r="K86" s="23" t="n">
         <f aca="false">IF(OR(D86="",E86="",D86=0),"",E86/D86)</f>
-        <v>5.88631012445341E-005</v>
+        <v>6.51811570586537E-005</v>
       </c>
       <c r="L86" s="24" t="n">
         <f aca="false">IF(OR(D86="",F86="",D86=0),"",F86/D86)</f>
-        <v>0.00402791792801884</v>
+        <v>0.00383637667259505</v>
       </c>
       <c r="M86" s="24" t="n">
         <f aca="false">IF(OR(D86="",G86="",D86=0),"",G86/D86)</f>
-        <v>0.0010427177934746</v>
+        <v>0.00162021733260082</v>
       </c>
       <c r="N86" s="24" t="n">
         <f aca="false">IF(OR(D86="",H86="",D86=0),"",H86/D86)</f>
-        <v>0.000992263706693576</v>
+        <v>0.000959094168148762</v>
       </c>
       <c r="O86" s="23" t="n">
         <f aca="false">IF(OR(D86="",I86="",D86=0),"",I86/D86)</f>
-        <v>8.40901446350488E-006</v>
+        <v>9.31159386552196E-006</v>
       </c>
       <c r="P86" s="24" t="n">
         <f aca="false">IF(OR(D86="",J86="",D86=0),"",J86/D86)</f>
-        <v>0.00613017154389506</v>
+        <v>0.00649018092426881</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3739,50 +4487,50 @@
         <v>46264</v>
       </c>
       <c r="D87" s="30" t="n">
-        <v>112911</v>
+        <v>116898</v>
       </c>
       <c r="E87" s="30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F87" s="30" t="n">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="G87" s="30" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H87" s="30" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="I87" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" s="10" t="n">
         <f aca="false">IF(COUNT(E87:I87)=0,"",SUM(E87:I87))</f>
-        <v>674</v>
+        <v>633</v>
       </c>
       <c r="K87" s="23" t="n">
         <f aca="false">IF(OR(D87="",E87="",D87=0),"",E87/D87)</f>
-        <v>7.0852264172667E-005</v>
+        <v>5.13267977210902E-005</v>
       </c>
       <c r="L87" s="24" t="n">
         <f aca="false">IF(OR(D87="",F87="",D87=0),"",F87/D87)</f>
-        <v>0.0033566260151801</v>
+        <v>0.00334479631815771</v>
       </c>
       <c r="M87" s="24" t="n">
         <f aca="false">IF(OR(D87="",G87="",D87=0),"",G87/D87)</f>
-        <v>0.00106278396259</v>
+        <v>0.0013259422744615</v>
       </c>
       <c r="N87" s="24" t="n">
         <f aca="false">IF(OR(D87="",H87="",D87=0),"",H87/D87)</f>
-        <v>0.00146132794856126</v>
+        <v>0.000684357302947869</v>
       </c>
       <c r="O87" s="23" t="n">
         <f aca="false">IF(OR(D87="",I87="",D87=0),"",I87/D87)</f>
-        <v>1.77130660431667E-005</v>
+        <v>8.55446628684836E-006</v>
       </c>
       <c r="P87" s="24" t="n">
         <f aca="false">IF(OR(D87="",J87="",D87=0),"",J87/D87)</f>
-        <v>0.00596930325654719</v>
+        <v>0.00541497715957501</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3797,39 +4545,51 @@
         <f aca="false">B88+6</f>
         <v>46271</v>
       </c>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
-      <c r="H88" s="30"/>
-      <c r="I88" s="30"/>
-      <c r="J88" s="10" t="str">
+      <c r="D88" s="30" t="n">
+        <v>109740</v>
+      </c>
+      <c r="E88" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="30" t="n">
+        <v>361</v>
+      </c>
+      <c r="G88" s="30" t="n">
+        <v>145</v>
+      </c>
+      <c r="H88" s="30" t="n">
+        <v>103</v>
+      </c>
+      <c r="I88" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="10" t="n">
         <f aca="false">IF(COUNT(E88:I88)=0,"",SUM(E88:I88))</f>
-        <v/>
-      </c>
-      <c r="K88" s="23" t="str">
+        <v>617</v>
+      </c>
+      <c r="K88" s="23" t="n">
         <f aca="false">IF(OR(D88="",E88="",D88=0),"",E88/D88)</f>
-        <v/>
-      </c>
-      <c r="L88" s="24" t="str">
+        <v>5.46746856205577E-005</v>
+      </c>
+      <c r="L88" s="24" t="n">
         <f aca="false">IF(OR(D88="",F88="",D88=0),"",F88/D88)</f>
-        <v/>
-      </c>
-      <c r="M88" s="24" t="str">
+        <v>0.00328959358483689</v>
+      </c>
+      <c r="M88" s="24" t="n">
         <f aca="false">IF(OR(D88="",G88="",D88=0),"",G88/D88)</f>
-        <v/>
-      </c>
-      <c r="N88" s="24" t="str">
+        <v>0.00132130490249681</v>
+      </c>
+      <c r="N88" s="24" t="n">
         <f aca="false">IF(OR(D88="",H88="",D88=0),"",H88/D88)</f>
-        <v/>
-      </c>
-      <c r="O88" s="23" t="str">
+        <v>0.000938582103152907</v>
+      </c>
+      <c r="O88" s="23" t="n">
         <f aca="false">IF(OR(D88="",I88="",D88=0),"",I88/D88)</f>
-        <v/>
-      </c>
-      <c r="P88" s="24" t="str">
+        <v>1.82248952068526E-005</v>
+      </c>
+      <c r="P88" s="24" t="n">
         <f aca="false">IF(OR(D88="",J88="",D88=0),"",J88/D88)</f>
-        <v/>
+        <v>0.00562238017131402</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3844,39 +4604,51 @@
         <f aca="false">B89+6</f>
         <v>46278</v>
       </c>
-      <c r="D89" s="30"/>
-      <c r="E89" s="30"/>
-      <c r="F89" s="30"/>
-      <c r="G89" s="30"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="30"/>
-      <c r="J89" s="10" t="str">
+      <c r="D89" s="30" t="n">
+        <v>106757</v>
+      </c>
+      <c r="E89" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" s="30" t="n">
+        <v>400</v>
+      </c>
+      <c r="G89" s="30" t="n">
+        <v>177</v>
+      </c>
+      <c r="H89" s="30" t="n">
+        <v>146</v>
+      </c>
+      <c r="I89" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="10" t="n">
         <f aca="false">IF(COUNT(E89:I89)=0,"",SUM(E89:I89))</f>
-        <v/>
-      </c>
-      <c r="K89" s="23" t="str">
+        <v>730</v>
+      </c>
+      <c r="K89" s="23" t="n">
         <f aca="false">IF(OR(D89="",E89="",D89=0),"",E89/D89)</f>
-        <v/>
-      </c>
-      <c r="L89" s="24" t="str">
+        <v>5.62024035894602E-005</v>
+      </c>
+      <c r="L89" s="24" t="n">
         <f aca="false">IF(OR(D89="",F89="",D89=0),"",F89/D89)</f>
-        <v/>
-      </c>
-      <c r="M89" s="24" t="str">
+        <v>0.00374682690596401</v>
+      </c>
+      <c r="M89" s="24" t="n">
         <f aca="false">IF(OR(D89="",G89="",D89=0),"",G89/D89)</f>
-        <v/>
-      </c>
-      <c r="N89" s="24" t="str">
+        <v>0.00165797090588908</v>
+      </c>
+      <c r="N89" s="24" t="n">
         <f aca="false">IF(OR(D89="",H89="",D89=0),"",H89/D89)</f>
-        <v/>
-      </c>
-      <c r="O89" s="23" t="str">
+        <v>0.00136759182067686</v>
+      </c>
+      <c r="O89" s="23" t="n">
         <f aca="false">IF(OR(D89="",I89="",D89=0),"",I89/D89)</f>
-        <v/>
-      </c>
-      <c r="P89" s="24" t="str">
+        <v>9.36706726491003E-006</v>
+      </c>
+      <c r="P89" s="24" t="n">
         <f aca="false">IF(OR(D89="",J89="",D89=0),"",J89/D89)</f>
-        <v/>
+        <v>0.00683795910338432</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,39 +4663,51 @@
         <f aca="false">B90+6</f>
         <v>46285</v>
       </c>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="30"/>
-      <c r="H90" s="30"/>
-      <c r="I90" s="30"/>
-      <c r="J90" s="10" t="str">
+      <c r="D90" s="30" t="n">
+        <v>101131</v>
+      </c>
+      <c r="E90" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="30" t="n">
+        <v>359</v>
+      </c>
+      <c r="G90" s="30" t="n">
+        <v>167</v>
+      </c>
+      <c r="H90" s="30" t="n">
+        <v>133</v>
+      </c>
+      <c r="I90" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="10" t="n">
         <f aca="false">IF(COUNT(E90:I90)=0,"",SUM(E90:I90))</f>
-        <v/>
-      </c>
-      <c r="K90" s="23" t="str">
+        <v>665</v>
+      </c>
+      <c r="K90" s="23" t="n">
         <f aca="false">IF(OR(D90="",E90="",D90=0),"",E90/D90)</f>
-        <v/>
-      </c>
-      <c r="L90" s="24" t="str">
+        <v>4.94408242774224E-005</v>
+      </c>
+      <c r="L90" s="24" t="n">
         <f aca="false">IF(OR(D90="",F90="",D90=0),"",F90/D90)</f>
-        <v/>
-      </c>
-      <c r="M90" s="24" t="str">
+        <v>0.00354985118311893</v>
+      </c>
+      <c r="M90" s="24" t="n">
         <f aca="false">IF(OR(D90="",G90="",D90=0),"",G90/D90)</f>
-        <v/>
-      </c>
-      <c r="N90" s="24" t="str">
+        <v>0.00165132353086591</v>
+      </c>
+      <c r="N90" s="24" t="n">
         <f aca="false">IF(OR(D90="",H90="",D90=0),"",H90/D90)</f>
-        <v/>
-      </c>
-      <c r="O90" s="23" t="str">
+        <v>0.00131512592577943</v>
+      </c>
+      <c r="O90" s="23" t="n">
         <f aca="false">IF(OR(D90="",I90="",D90=0),"",I90/D90)</f>
-        <v/>
-      </c>
-      <c r="P90" s="24" t="str">
+        <v>9.88816485548447E-006</v>
+      </c>
+      <c r="P90" s="24" t="n">
         <f aca="false">IF(OR(D90="",J90="",D90=0),"",J90/D90)</f>
-        <v/>
+        <v>0.00657562962889717</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3938,39 +4722,51 @@
         <f aca="false">B91+6</f>
         <v>46292</v>
       </c>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
-      <c r="I91" s="30"/>
-      <c r="J91" s="10" t="str">
+      <c r="D91" s="30" t="n">
+        <v>103931</v>
+      </c>
+      <c r="E91" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="30" t="n">
+        <v>365</v>
+      </c>
+      <c r="G91" s="30" t="n">
+        <v>202</v>
+      </c>
+      <c r="H91" s="30" t="n">
+        <v>156</v>
+      </c>
+      <c r="I91" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="10" t="n">
         <f aca="false">IF(COUNT(E91:I91)=0,"",SUM(E91:I91))</f>
-        <v/>
-      </c>
-      <c r="K91" s="23" t="str">
+        <v>729</v>
+      </c>
+      <c r="K91" s="23" t="n">
         <f aca="false">IF(OR(D91="",E91="",D91=0),"",E91/D91)</f>
-        <v/>
-      </c>
-      <c r="L91" s="24" t="str">
+        <v>4.81088414428804E-005</v>
+      </c>
+      <c r="L91" s="24" t="n">
         <f aca="false">IF(OR(D91="",F91="",D91=0),"",F91/D91)</f>
-        <v/>
-      </c>
-      <c r="M91" s="24" t="str">
+        <v>0.00351194542533027</v>
+      </c>
+      <c r="M91" s="24" t="n">
         <f aca="false">IF(OR(D91="",G91="",D91=0),"",G91/D91)</f>
-        <v/>
-      </c>
-      <c r="N91" s="24" t="str">
+        <v>0.00194359719429237</v>
+      </c>
+      <c r="N91" s="24" t="n">
         <f aca="false">IF(OR(D91="",H91="",D91=0),"",H91/D91)</f>
-        <v/>
-      </c>
-      <c r="O91" s="23" t="str">
+        <v>0.00150099585301787</v>
+      </c>
+      <c r="O91" s="23" t="n">
         <f aca="false">IF(OR(D91="",I91="",D91=0),"",I91/D91)</f>
-        <v/>
-      </c>
-      <c r="P91" s="24" t="str">
+        <v>9.62176828857607E-006</v>
+      </c>
+      <c r="P91" s="24" t="n">
         <f aca="false">IF(OR(D91="",J91="",D91=0),"",J91/D91)</f>
-        <v/>
+        <v>0.00701426908237196</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3985,39 +4781,51 @@
         <f aca="false">B92+6</f>
         <v>46299</v>
       </c>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="30"/>
-      <c r="J92" s="10" t="str">
+      <c r="D92" s="30" t="n">
+        <v>96072</v>
+      </c>
+      <c r="E92" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="30" t="n">
+        <v>455</v>
+      </c>
+      <c r="G92" s="30" t="n">
+        <v>161</v>
+      </c>
+      <c r="H92" s="30" t="n">
+        <v>97</v>
+      </c>
+      <c r="I92" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="10" t="n">
         <f aca="false">IF(COUNT(E92:I92)=0,"",SUM(E92:I92))</f>
-        <v/>
-      </c>
-      <c r="K92" s="23" t="str">
+        <v>719</v>
+      </c>
+      <c r="K92" s="23" t="n">
         <f aca="false">IF(OR(D92="",E92="",D92=0),"",E92/D92)</f>
-        <v/>
-      </c>
-      <c r="L92" s="24" t="str">
+        <v>5.20443001082521E-005</v>
+      </c>
+      <c r="L92" s="24" t="n">
         <f aca="false">IF(OR(D92="",F92="",D92=0),"",F92/D92)</f>
-        <v/>
-      </c>
-      <c r="M92" s="24" t="str">
+        <v>0.00473603130985095</v>
+      </c>
+      <c r="M92" s="24" t="n">
         <f aca="false">IF(OR(D92="",G92="",D92=0),"",G92/D92)</f>
-        <v/>
-      </c>
-      <c r="N92" s="24" t="str">
+        <v>0.00167582646348572</v>
+      </c>
+      <c r="N92" s="24" t="n">
         <f aca="false">IF(OR(D92="",H92="",D92=0),"",H92/D92)</f>
-        <v/>
-      </c>
-      <c r="O92" s="23" t="str">
+        <v>0.00100965942210009</v>
+      </c>
+      <c r="O92" s="23" t="n">
         <f aca="false">IF(OR(D92="",I92="",D92=0),"",I92/D92)</f>
-        <v/>
-      </c>
-      <c r="P92" s="24" t="str">
+        <v>1.04088600216504E-005</v>
+      </c>
+      <c r="P92" s="24" t="n">
         <f aca="false">IF(OR(D92="",J92="",D92=0),"",J92/D92)</f>
-        <v/>
+        <v>0.00748397035556666</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4032,39 +4840,51 @@
         <f aca="false">B93+6</f>
         <v>46306</v>
       </c>
-      <c r="D93" s="30"/>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
-      <c r="H93" s="30"/>
-      <c r="I93" s="30"/>
-      <c r="J93" s="10" t="str">
+      <c r="D93" s="30" t="n">
+        <v>113958</v>
+      </c>
+      <c r="E93" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" s="30" t="n">
+        <v>402</v>
+      </c>
+      <c r="G93" s="30" t="n">
+        <v>162</v>
+      </c>
+      <c r="H93" s="30" t="n">
+        <v>136</v>
+      </c>
+      <c r="I93" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="10" t="n">
         <f aca="false">IF(COUNT(E93:I93)=0,"",SUM(E93:I93))</f>
-        <v/>
-      </c>
-      <c r="K93" s="23" t="str">
+        <v>708</v>
+      </c>
+      <c r="K93" s="23" t="n">
         <f aca="false">IF(OR(D93="",E93="",D93=0),"",E93/D93)</f>
-        <v/>
-      </c>
-      <c r="L93" s="24" t="str">
+        <v>6.14261394548869E-005</v>
+      </c>
+      <c r="L93" s="24" t="n">
         <f aca="false">IF(OR(D93="",F93="",D93=0),"",F93/D93)</f>
-        <v/>
-      </c>
-      <c r="M93" s="24" t="str">
+        <v>0.00352761543726636</v>
+      </c>
+      <c r="M93" s="24" t="n">
         <f aca="false">IF(OR(D93="",G93="",D93=0),"",G93/D93)</f>
-        <v/>
-      </c>
-      <c r="N93" s="24" t="str">
+        <v>0.00142157637024167</v>
+      </c>
+      <c r="N93" s="24" t="n">
         <f aca="false">IF(OR(D93="",H93="",D93=0),"",H93/D93)</f>
-        <v/>
-      </c>
-      <c r="O93" s="23" t="str">
+        <v>0.00119342213798066</v>
+      </c>
+      <c r="O93" s="23" t="n">
         <f aca="false">IF(OR(D93="",I93="",D93=0),"",I93/D93)</f>
-        <v/>
-      </c>
-      <c r="P93" s="24" t="str">
+        <v>8.77516277926956E-006</v>
+      </c>
+      <c r="P93" s="24" t="n">
         <f aca="false">IF(OR(D93="",J93="",D93=0),"",J93/D93)</f>
-        <v/>
+        <v>0.00621281524772285</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4079,39 +4899,51 @@
         <f aca="false">B94+6</f>
         <v>46313</v>
       </c>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="30"/>
-      <c r="J94" s="10" t="str">
+      <c r="D94" s="30" t="n">
+        <v>111533</v>
+      </c>
+      <c r="E94" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F94" s="30" t="n">
+        <v>266</v>
+      </c>
+      <c r="G94" s="30" t="n">
+        <v>175</v>
+      </c>
+      <c r="H94" s="30" t="n">
+        <v>141</v>
+      </c>
+      <c r="I94" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="10" t="n">
         <f aca="false">IF(COUNT(E94:I94)=0,"",SUM(E94:I94))</f>
-        <v/>
-      </c>
-      <c r="K94" s="23" t="str">
+        <v>591</v>
+      </c>
+      <c r="K94" s="23" t="n">
         <f aca="false">IF(OR(D94="",E94="",D94=0),"",E94/D94)</f>
-        <v/>
-      </c>
-      <c r="L94" s="24" t="str">
+        <v>6.27616938484574E-005</v>
+      </c>
+      <c r="L94" s="24" t="n">
         <f aca="false">IF(OR(D94="",F94="",D94=0),"",F94/D94)</f>
-        <v/>
-      </c>
-      <c r="M94" s="24" t="str">
+        <v>0.00238494436624138</v>
+      </c>
+      <c r="M94" s="24" t="n">
         <f aca="false">IF(OR(D94="",G94="",D94=0),"",G94/D94)</f>
-        <v/>
-      </c>
-      <c r="N94" s="24" t="str">
+        <v>0.00156904234621144</v>
+      </c>
+      <c r="N94" s="24" t="n">
         <f aca="false">IF(OR(D94="",H94="",D94=0),"",H94/D94)</f>
-        <v/>
-      </c>
-      <c r="O94" s="23" t="str">
+        <v>0.00126419983323321</v>
+      </c>
+      <c r="O94" s="23" t="n">
         <f aca="false">IF(OR(D94="",I94="",D94=0),"",I94/D94)</f>
-        <v/>
-      </c>
-      <c r="P94" s="24" t="str">
+        <v>1.79319125281307E-005</v>
+      </c>
+      <c r="P94" s="24" t="n">
         <f aca="false">IF(OR(D94="",J94="",D94=0),"",J94/D94)</f>
-        <v/>
+        <v>0.00529888015206262</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4126,39 +4958,51 @@
         <f aca="false">B95+6</f>
         <v>46320</v>
       </c>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="30"/>
-      <c r="J95" s="10" t="str">
+      <c r="D95" s="30" t="n">
+        <v>95764</v>
+      </c>
+      <c r="E95" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="30" t="n">
+        <v>372</v>
+      </c>
+      <c r="G95" s="30" t="n">
+        <v>132</v>
+      </c>
+      <c r="H95" s="30" t="n">
+        <v>141</v>
+      </c>
+      <c r="I95" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" s="10" t="n">
         <f aca="false">IF(COUNT(E95:I95)=0,"",SUM(E95:I95))</f>
-        <v/>
-      </c>
-      <c r="K95" s="23" t="str">
+        <v>652</v>
+      </c>
+      <c r="K95" s="23" t="n">
         <f aca="false">IF(OR(D95="",E95="",D95=0),"",E95/D95)</f>
-        <v/>
-      </c>
-      <c r="L95" s="24" t="str">
+        <v>5.22116870640324E-005</v>
+      </c>
+      <c r="L95" s="24" t="n">
         <f aca="false">IF(OR(D95="",F95="",D95=0),"",F95/D95)</f>
-        <v/>
-      </c>
-      <c r="M95" s="24" t="str">
+        <v>0.00388454951756401</v>
+      </c>
+      <c r="M95" s="24" t="n">
         <f aca="false">IF(OR(D95="",G95="",D95=0),"",G95/D95)</f>
-        <v/>
-      </c>
-      <c r="N95" s="24" t="str">
+        <v>0.00137838853849046</v>
+      </c>
+      <c r="N95" s="24" t="n">
         <f aca="false">IF(OR(D95="",H95="",D95=0),"",H95/D95)</f>
-        <v/>
-      </c>
-      <c r="O95" s="23" t="str">
+        <v>0.00147236957520571</v>
+      </c>
+      <c r="O95" s="23" t="n">
         <f aca="false">IF(OR(D95="",I95="",D95=0),"",I95/D95)</f>
-        <v/>
-      </c>
-      <c r="P95" s="24" t="str">
+        <v>2.0884674825613E-005</v>
+      </c>
+      <c r="P95" s="24" t="n">
         <f aca="false">IF(OR(D95="",J95="",D95=0),"",J95/D95)</f>
-        <v/>
+        <v>0.00680840399314983</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,39 +5017,51 @@
         <f aca="false">B96+6</f>
         <v>46327</v>
       </c>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="30"/>
-      <c r="J96" s="10" t="str">
+      <c r="D96" s="30" t="n">
+        <v>93118</v>
+      </c>
+      <c r="E96" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" s="30" t="n">
+        <v>406</v>
+      </c>
+      <c r="G96" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="H96" s="30" t="n">
+        <v>153</v>
+      </c>
+      <c r="I96" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="10" t="n">
         <f aca="false">IF(COUNT(E96:I96)=0,"",SUM(E96:I96))</f>
-        <v/>
-      </c>
-      <c r="K96" s="23" t="str">
+        <v>757</v>
+      </c>
+      <c r="K96" s="23" t="n">
         <f aca="false">IF(OR(D96="",E96="",D96=0),"",E96/D96)</f>
-        <v/>
-      </c>
-      <c r="L96" s="24" t="str">
+        <v>6.44343735904981E-005</v>
+      </c>
+      <c r="L96" s="24" t="n">
         <f aca="false">IF(OR(D96="",F96="",D96=0),"",F96/D96)</f>
-        <v/>
-      </c>
-      <c r="M96" s="24" t="str">
+        <v>0.0043600592796237</v>
+      </c>
+      <c r="M96" s="24" t="n">
         <f aca="false">IF(OR(D96="",G96="",D96=0),"",G96/D96)</f>
-        <v/>
-      </c>
-      <c r="N96" s="24" t="str">
+        <v>0.00204042183036577</v>
+      </c>
+      <c r="N96" s="24" t="n">
         <f aca="false">IF(OR(D96="",H96="",D96=0),"",H96/D96)</f>
-        <v/>
-      </c>
-      <c r="O96" s="23" t="str">
+        <v>0.0016430765265577</v>
+      </c>
+      <c r="O96" s="23" t="n">
         <f aca="false">IF(OR(D96="",I96="",D96=0),"",I96/D96)</f>
-        <v/>
-      </c>
-      <c r="P96" s="24" t="str">
+        <v>2.1478124530166E-005</v>
+      </c>
+      <c r="P96" s="24" t="n">
         <f aca="false">IF(OR(D96="",J96="",D96=0),"",J96/D96)</f>
-        <v/>
+        <v>0.00812947013466784</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4220,39 +5076,51 @@
         <f aca="false">B97+6</f>
         <v>46334</v>
       </c>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="30"/>
-      <c r="J97" s="10" t="str">
+      <c r="D97" s="30" t="n">
+        <v>99072</v>
+      </c>
+      <c r="E97" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" s="30" t="n">
+        <v>402</v>
+      </c>
+      <c r="G97" s="30" t="n">
+        <v>188</v>
+      </c>
+      <c r="H97" s="30" t="n">
+        <v>149</v>
+      </c>
+      <c r="I97" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="10" t="n">
         <f aca="false">IF(COUNT(E97:I97)=0,"",SUM(E97:I97))</f>
-        <v/>
-      </c>
-      <c r="K97" s="23" t="str">
+        <v>747</v>
+      </c>
+      <c r="K97" s="23" t="n">
         <f aca="false">IF(OR(D97="",E97="",D97=0),"",E97/D97)</f>
-        <v/>
-      </c>
-      <c r="L97" s="24" t="str">
+        <v>7.0655684754522E-005</v>
+      </c>
+      <c r="L97" s="24" t="n">
         <f aca="false">IF(OR(D97="",F97="",D97=0),"",F97/D97)</f>
-        <v/>
-      </c>
-      <c r="M97" s="24" t="str">
+        <v>0.00405765503875969</v>
+      </c>
+      <c r="M97" s="24" t="n">
         <f aca="false">IF(OR(D97="",G97="",D97=0),"",G97/D97)</f>
-        <v/>
-      </c>
-      <c r="N97" s="24" t="str">
+        <v>0.00189760981912145</v>
+      </c>
+      <c r="N97" s="24" t="n">
         <f aca="false">IF(OR(D97="",H97="",D97=0),"",H97/D97)</f>
-        <v/>
-      </c>
-      <c r="O97" s="23" t="str">
+        <v>0.00150395671834625</v>
+      </c>
+      <c r="O97" s="23" t="n">
         <f aca="false">IF(OR(D97="",I97="",D97=0),"",I97/D97)</f>
-        <v/>
-      </c>
-      <c r="P97" s="24" t="str">
+        <v>1.0093669250646E-005</v>
+      </c>
+      <c r="P97" s="24" t="n">
         <f aca="false">IF(OR(D97="",J97="",D97=0),"",J97/D97)</f>
-        <v/>
+        <v>0.00753997093023256</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4267,39 +5135,51 @@
         <f aca="false">B98+6</f>
         <v>46341</v>
       </c>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="30"/>
-      <c r="J98" s="10" t="str">
+      <c r="D98" s="30" t="n">
+        <v>100312</v>
+      </c>
+      <c r="E98" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="30" t="n">
+        <v>506</v>
+      </c>
+      <c r="G98" s="30" t="n">
+        <v>167</v>
+      </c>
+      <c r="H98" s="30" t="n">
+        <v>93</v>
+      </c>
+      <c r="I98" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="10" t="n">
         <f aca="false">IF(COUNT(E98:I98)=0,"",SUM(E98:I98))</f>
-        <v/>
-      </c>
-      <c r="K98" s="23" t="str">
+        <v>775</v>
+      </c>
+      <c r="K98" s="23" t="n">
         <f aca="false">IF(OR(D98="",E98="",D98=0),"",E98/D98)</f>
-        <v/>
-      </c>
-      <c r="L98" s="24" t="str">
+        <v>7.97511763298509E-005</v>
+      </c>
+      <c r="L98" s="24" t="n">
         <f aca="false">IF(OR(D98="",F98="",D98=0),"",F98/D98)</f>
-        <v/>
-      </c>
-      <c r="M98" s="24" t="str">
+        <v>0.00504426190286307</v>
+      </c>
+      <c r="M98" s="24" t="n">
         <f aca="false">IF(OR(D98="",G98="",D98=0),"",G98/D98)</f>
-        <v/>
-      </c>
-      <c r="N98" s="24" t="str">
+        <v>0.00166480580588564</v>
+      </c>
+      <c r="N98" s="24" t="n">
         <f aca="false">IF(OR(D98="",H98="",D98=0),"",H98/D98)</f>
-        <v/>
-      </c>
-      <c r="O98" s="23" t="str">
+        <v>0.000927107424834516</v>
+      </c>
+      <c r="O98" s="23" t="n">
         <f aca="false">IF(OR(D98="",I98="",D98=0),"",I98/D98)</f>
-        <v/>
-      </c>
-      <c r="P98" s="24" t="str">
+        <v>9.96889704123136E-006</v>
+      </c>
+      <c r="P98" s="24" t="n">
         <f aca="false">IF(OR(D98="",J98="",D98=0),"",J98/D98)</f>
-        <v/>
+        <v>0.0077258952069543</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4314,39 +5194,51 @@
         <f aca="false">B99+6</f>
         <v>46348</v>
       </c>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
-      <c r="J99" s="10" t="str">
+      <c r="D99" s="30" t="n">
+        <v>108756</v>
+      </c>
+      <c r="E99" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F99" s="30" t="n">
+        <v>456</v>
+      </c>
+      <c r="G99" s="30" t="n">
+        <v>131</v>
+      </c>
+      <c r="H99" s="30" t="n">
+        <v>131</v>
+      </c>
+      <c r="I99" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="10" t="n">
         <f aca="false">IF(COUNT(E99:I99)=0,"",SUM(E99:I99))</f>
-        <v/>
-      </c>
-      <c r="K99" s="23" t="str">
+        <v>726</v>
+      </c>
+      <c r="K99" s="23" t="n">
         <f aca="false">IF(OR(D99="",E99="",D99=0),"",E99/D99)</f>
-        <v/>
-      </c>
-      <c r="L99" s="24" t="str">
+        <v>6.43642649600942E-005</v>
+      </c>
+      <c r="L99" s="24" t="n">
         <f aca="false">IF(OR(D99="",F99="",D99=0),"",F99/D99)</f>
-        <v/>
-      </c>
-      <c r="M99" s="24" t="str">
+        <v>0.00419287211740042</v>
+      </c>
+      <c r="M99" s="24" t="n">
         <f aca="false">IF(OR(D99="",G99="",D99=0),"",G99/D99)</f>
-        <v/>
-      </c>
-      <c r="N99" s="24" t="str">
+        <v>0.00120453124425319</v>
+      </c>
+      <c r="N99" s="24" t="n">
         <f aca="false">IF(OR(D99="",H99="",D99=0),"",H99/D99)</f>
-        <v/>
-      </c>
-      <c r="O99" s="23" t="str">
+        <v>0.00120453124425319</v>
+      </c>
+      <c r="O99" s="23" t="n">
         <f aca="false">IF(OR(D99="",I99="",D99=0),"",I99/D99)</f>
-        <v/>
-      </c>
-      <c r="P99" s="24" t="str">
+        <v>9.19489499429917E-006</v>
+      </c>
+      <c r="P99" s="24" t="n">
         <f aca="false">IF(OR(D99="",J99="",D99=0),"",J99/D99)</f>
-        <v/>
+        <v>0.00667549376586119</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4361,39 +5253,51 @@
         <f aca="false">B100+6</f>
         <v>46355</v>
       </c>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
-      <c r="J100" s="10" t="str">
+      <c r="D100" s="30" t="n">
+        <v>106103</v>
+      </c>
+      <c r="E100" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="30" t="n">
+        <v>391</v>
+      </c>
+      <c r="G100" s="30" t="n">
+        <v>167</v>
+      </c>
+      <c r="H100" s="30" t="n">
+        <v>131</v>
+      </c>
+      <c r="I100" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="10" t="n">
         <f aca="false">IF(COUNT(E100:I100)=0,"",SUM(E100:I100))</f>
-        <v/>
-      </c>
-      <c r="K100" s="23" t="str">
+        <v>698</v>
+      </c>
+      <c r="K100" s="23" t="n">
         <f aca="false">IF(OR(D100="",E100="",D100=0),"",E100/D100)</f>
-        <v/>
-      </c>
-      <c r="L100" s="24" t="str">
+        <v>6.59736293978493E-005</v>
+      </c>
+      <c r="L100" s="24" t="n">
         <f aca="false">IF(OR(D100="",F100="",D100=0),"",F100/D100)</f>
-        <v/>
-      </c>
-      <c r="M100" s="24" t="str">
+        <v>0.00368509844207987</v>
+      </c>
+      <c r="M100" s="24" t="n">
         <f aca="false">IF(OR(D100="",G100="",D100=0),"",G100/D100)</f>
-        <v/>
-      </c>
-      <c r="N100" s="24" t="str">
+        <v>0.00157394230134869</v>
+      </c>
+      <c r="N100" s="24" t="n">
         <f aca="false">IF(OR(D100="",H100="",D100=0),"",H100/D100)</f>
-        <v/>
-      </c>
-      <c r="O100" s="23" t="str">
+        <v>0.00123464935015975</v>
+      </c>
+      <c r="O100" s="23" t="n">
         <f aca="false">IF(OR(D100="",I100="",D100=0),"",I100/D100)</f>
-        <v/>
-      </c>
-      <c r="P100" s="24" t="str">
+        <v>1.88496083993855E-005</v>
+      </c>
+      <c r="P100" s="24" t="n">
         <f aca="false">IF(OR(D100="",J100="",D100=0),"",J100/D100)</f>
-        <v/>
+        <v>0.00657851333138554</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4408,39 +5312,51 @@
         <f aca="false">B101+6</f>
         <v>46362</v>
       </c>
-      <c r="D101" s="30"/>
-      <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-      <c r="H101" s="30"/>
-      <c r="I101" s="30"/>
-      <c r="J101" s="10" t="str">
+      <c r="D101" s="30" t="n">
+        <v>104608</v>
+      </c>
+      <c r="E101" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="30" t="n">
+        <v>325</v>
+      </c>
+      <c r="G101" s="30" t="n">
+        <v>175</v>
+      </c>
+      <c r="H101" s="30" t="n">
+        <v>153</v>
+      </c>
+      <c r="I101" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="10" t="n">
         <f aca="false">IF(COUNT(E101:I101)=0,"",SUM(E101:I101))</f>
-        <v/>
-      </c>
-      <c r="K101" s="23" t="str">
+        <v>661</v>
+      </c>
+      <c r="K101" s="23" t="n">
         <f aca="false">IF(OR(D101="",E101="",D101=0),"",E101/D101)</f>
-        <v/>
-      </c>
-      <c r="L101" s="24" t="str">
+        <v>5.73569899051698E-005</v>
+      </c>
+      <c r="L101" s="24" t="n">
         <f aca="false">IF(OR(D101="",F101="",D101=0),"",F101/D101)</f>
-        <v/>
-      </c>
-      <c r="M101" s="24" t="str">
+        <v>0.0031068369531967</v>
+      </c>
+      <c r="M101" s="24" t="n">
         <f aca="false">IF(OR(D101="",G101="",D101=0),"",G101/D101)</f>
-        <v/>
-      </c>
-      <c r="N101" s="24" t="str">
+        <v>0.00167291220556745</v>
+      </c>
+      <c r="N101" s="24" t="n">
         <f aca="false">IF(OR(D101="",H101="",D101=0),"",H101/D101)</f>
-        <v/>
-      </c>
-      <c r="O101" s="23" t="str">
+        <v>0.00146260324258183</v>
+      </c>
+      <c r="O101" s="23" t="n">
         <f aca="false">IF(OR(D101="",I101="",D101=0),"",I101/D101)</f>
-        <v/>
-      </c>
-      <c r="P101" s="24" t="str">
+        <v>1.91189966350566E-005</v>
+      </c>
+      <c r="P101" s="24" t="n">
         <f aca="false">IF(OR(D101="",J101="",D101=0),"",J101/D101)</f>
-        <v/>
+        <v>0.0063188283878862</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4455,39 +5371,51 @@
         <f aca="false">B102+6</f>
         <v>46369</v>
       </c>
-      <c r="D102" s="30"/>
-      <c r="E102" s="30"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
-      <c r="H102" s="30"/>
-      <c r="I102" s="30"/>
-      <c r="J102" s="10" t="str">
+      <c r="D102" s="30" t="n">
+        <v>101748</v>
+      </c>
+      <c r="E102" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" s="30" t="n">
+        <v>473</v>
+      </c>
+      <c r="G102" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="H102" s="30" t="n">
+        <v>141</v>
+      </c>
+      <c r="I102" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="10" t="n">
         <f aca="false">IF(COUNT(E102:I102)=0,"",SUM(E102:I102))</f>
-        <v/>
-      </c>
-      <c r="K102" s="23" t="str">
+        <v>821</v>
+      </c>
+      <c r="K102" s="23" t="n">
         <f aca="false">IF(OR(D102="",E102="",D102=0),"",E102/D102)</f>
-        <v/>
-      </c>
-      <c r="L102" s="24" t="str">
+        <v>5.89692180681684E-005</v>
+      </c>
+      <c r="L102" s="24" t="n">
         <f aca="false">IF(OR(D102="",F102="",D102=0),"",F102/D102)</f>
-        <v/>
-      </c>
-      <c r="M102" s="24" t="str">
+        <v>0.00464874002437394</v>
+      </c>
+      <c r="M102" s="24" t="n">
         <f aca="false">IF(OR(D102="",G102="",D102=0),"",G102/D102)</f>
-        <v/>
-      </c>
-      <c r="N102" s="24" t="str">
+        <v>0.00196564060227228</v>
+      </c>
+      <c r="N102" s="24" t="n">
         <f aca="false">IF(OR(D102="",H102="",D102=0),"",H102/D102)</f>
-        <v/>
-      </c>
-      <c r="O102" s="23" t="str">
+        <v>0.00138577662460196</v>
+      </c>
+      <c r="O102" s="23" t="n">
         <f aca="false">IF(OR(D102="",I102="",D102=0),"",I102/D102)</f>
-        <v/>
-      </c>
-      <c r="P102" s="24" t="str">
+        <v>9.8282030113614E-006</v>
+      </c>
+      <c r="P102" s="24" t="n">
         <f aca="false">IF(OR(D102="",J102="",D102=0),"",J102/D102)</f>
-        <v/>
+        <v>0.00806895467232771</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4502,39 +5430,51 @@
         <f aca="false">B103+6</f>
         <v>46376</v>
       </c>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="30"/>
-      <c r="J103" s="10" t="str">
+      <c r="D103" s="30" t="n">
+        <v>98516</v>
+      </c>
+      <c r="E103" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" s="30" t="n">
+        <v>417</v>
+      </c>
+      <c r="G103" s="30" t="n">
+        <v>205</v>
+      </c>
+      <c r="H103" s="30" t="n">
+        <v>162</v>
+      </c>
+      <c r="I103" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="10" t="n">
         <f aca="false">IF(COUNT(E103:I103)=0,"",SUM(E103:I103))</f>
-        <v/>
-      </c>
-      <c r="K103" s="23" t="str">
+        <v>792</v>
+      </c>
+      <c r="K103" s="23" t="n">
         <f aca="false">IF(OR(D103="",E103="",D103=0),"",E103/D103)</f>
-        <v/>
-      </c>
-      <c r="L103" s="24" t="str">
+        <v>7.10544480084453E-005</v>
+      </c>
+      <c r="L103" s="24" t="n">
         <f aca="false">IF(OR(D103="",F103="",D103=0),"",F103/D103)</f>
-        <v/>
-      </c>
-      <c r="M103" s="24" t="str">
+        <v>0.00423281497421739</v>
+      </c>
+      <c r="M103" s="24" t="n">
         <f aca="false">IF(OR(D103="",G103="",D103=0),"",G103/D103)</f>
-        <v/>
-      </c>
-      <c r="N103" s="24" t="str">
+        <v>0.00208088026310447</v>
+      </c>
+      <c r="N103" s="24" t="n">
         <f aca="false">IF(OR(D103="",H103="",D103=0),"",H103/D103)</f>
-        <v/>
-      </c>
-      <c r="O103" s="23" t="str">
+        <v>0.00164440293962402</v>
+      </c>
+      <c r="O103" s="23" t="n">
         <f aca="false">IF(OR(D103="",I103="",D103=0),"",I103/D103)</f>
-        <v/>
-      </c>
-      <c r="P103" s="24" t="str">
+        <v>1.01506354297779E-005</v>
+      </c>
+      <c r="P103" s="24" t="n">
         <f aca="false">IF(OR(D103="",J103="",D103=0),"",J103/D103)</f>
-        <v/>
+        <v>0.0080393032603841</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4549,39 +5489,51 @@
         <f aca="false">B104+6</f>
         <v>46383</v>
       </c>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="30"/>
-      <c r="J104" s="10" t="str">
+      <c r="D104" s="30" t="n">
+        <v>99299</v>
+      </c>
+      <c r="E104" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F104" s="30" t="n">
+        <v>456</v>
+      </c>
+      <c r="G104" s="30" t="n">
+        <v>182</v>
+      </c>
+      <c r="H104" s="30" t="n">
+        <v>108</v>
+      </c>
+      <c r="I104" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="10" t="n">
         <f aca="false">IF(COUNT(E104:I104)=0,"",SUM(E104:I104))</f>
-        <v/>
-      </c>
-      <c r="K104" s="23" t="str">
+        <v>754</v>
+      </c>
+      <c r="K104" s="23" t="n">
         <f aca="false">IF(OR(D104="",E104="",D104=0),"",E104/D104)</f>
-        <v/>
-      </c>
-      <c r="L104" s="24" t="str">
+        <v>7.04941640902728E-005</v>
+      </c>
+      <c r="L104" s="24" t="n">
         <f aca="false">IF(OR(D104="",F104="",D104=0),"",F104/D104)</f>
-        <v/>
-      </c>
-      <c r="M104" s="24" t="str">
+        <v>0.00459219126073777</v>
+      </c>
+      <c r="M104" s="24" t="n">
         <f aca="false">IF(OR(D104="",G104="",D104=0),"",G104/D104)</f>
-        <v/>
-      </c>
-      <c r="N104" s="24" t="str">
+        <v>0.00183284826634709</v>
+      </c>
+      <c r="N104" s="24" t="n">
         <f aca="false">IF(OR(D104="",H104="",D104=0),"",H104/D104)</f>
-        <v/>
-      </c>
-      <c r="O104" s="23" t="str">
+        <v>0.00108762424596421</v>
+      </c>
+      <c r="O104" s="23" t="n">
         <f aca="false">IF(OR(D104="",I104="",D104=0),"",I104/D104)</f>
-        <v/>
-      </c>
-      <c r="P104" s="24" t="str">
+        <v>1.0070594870039E-005</v>
+      </c>
+      <c r="P104" s="24" t="n">
         <f aca="false">IF(OR(D104="",J104="",D104=0),"",J104/D104)</f>
-        <v/>
+        <v>0.00759322853200939</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4596,44 +5548,56 @@
         <f aca="false">B105+6</f>
         <v>46390</v>
       </c>
-      <c r="D105" s="30"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="30"/>
-      <c r="J105" s="10" t="str">
+      <c r="D105" s="30" t="n">
+        <v>110550</v>
+      </c>
+      <c r="E105" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F105" s="30" t="n">
+        <v>503</v>
+      </c>
+      <c r="G105" s="30" t="n">
+        <v>160</v>
+      </c>
+      <c r="H105" s="30" t="n">
+        <v>103</v>
+      </c>
+      <c r="I105" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="10" t="n">
         <f aca="false">IF(COUNT(E105:I105)=0,"",SUM(E105:I105))</f>
-        <v/>
-      </c>
-      <c r="K105" s="23" t="str">
+        <v>774</v>
+      </c>
+      <c r="K105" s="23" t="n">
         <f aca="false">IF(OR(D105="",E105="",D105=0),"",E105/D105)</f>
-        <v/>
-      </c>
-      <c r="L105" s="24" t="str">
+        <v>6.33197648123021E-005</v>
+      </c>
+      <c r="L105" s="24" t="n">
         <f aca="false">IF(OR(D105="",F105="",D105=0),"",F105/D105)</f>
-        <v/>
-      </c>
-      <c r="M105" s="24" t="str">
+        <v>0.00454997738579828</v>
+      </c>
+      <c r="M105" s="24" t="n">
         <f aca="false">IF(OR(D105="",G105="",D105=0),"",G105/D105)</f>
-        <v/>
-      </c>
-      <c r="N105" s="24" t="str">
+        <v>0.00144730890999548</v>
+      </c>
+      <c r="N105" s="24" t="n">
         <f aca="false">IF(OR(D105="",H105="",D105=0),"",H105/D105)</f>
-        <v/>
-      </c>
-      <c r="O105" s="23" t="str">
+        <v>0.000931705110809588</v>
+      </c>
+      <c r="O105" s="23" t="n">
         <f aca="false">IF(OR(D105="",I105="",D105=0),"",I105/D105)</f>
-        <v/>
-      </c>
-      <c r="P105" s="24" t="str">
+        <v>9.04568068747173E-006</v>
+      </c>
+      <c r="P105" s="24" t="n">
         <f aca="false">IF(OR(D105="",J105="",D105=0),"",J105/D105)</f>
-        <v/>
+        <v>0.00700135685210312</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4661,83 +5625,11 @@
       <formula>AND(ISNUMBER(F5),F5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16 E16 G16 I16 K16">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17 E17 G17 I17 K17">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18 E18 G18 I18 K18">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19 E19 G19 I19 K19">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20 E20 G20 I20 K20">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21 E21 G21 I21 K21">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F28:H33">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(F28),F28&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(F28),F28&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4769,18 +5661,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="31" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -4801,11 +5693,11 @@
         <v>15</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2" s="32" t="n">
         <f aca="false">COUNT('Досмотр по неделям'!$D$80:$D$105)</f>
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4815,38 +5707,38 @@
       </c>
       <c r="B3" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D80="",NA(),'Досмотр по неделям'!D80)</f>
-        <v>96451</v>
+        <v>97588</v>
       </c>
       <c r="C3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K80="",'Досмотр по неделям'!K80=0),NA(),'Досмотр по неделям'!K80)</f>
-        <v>6.22077531596355E-005</v>
+        <v>6.14829692175267E-005</v>
       </c>
       <c r="D3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L80="",'Досмотр по неделям'!L80=0),NA(),'Досмотр по неделям'!L80)</f>
-        <v>0.00300670806938238</v>
+        <v>0.00440627946058942</v>
       </c>
       <c r="E3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M80="",'Досмотр по неделям'!M80=0),NA(),'Досмотр по неделям'!M80)</f>
-        <v>0.00205285585426797</v>
+        <v>0.00197770217649711</v>
       </c>
       <c r="F3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N80="",'Досмотр по неделям'!N80=0),NA(),'Досмотр по неделям'!N80)</f>
-        <v>0.00124415506319271</v>
+        <v>0.00102471615362545</v>
       </c>
       <c r="G3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O80="",'Досмотр по неделям'!O80=0),NA(),'Досмотр по неделям'!O80)</f>
-        <v>1.03679588599392E-005</v>
+        <v>1.02471615362545E-005</v>
       </c>
       <c r="H3" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P80="",'Досмотр по неделям'!P80=0),NA(),'Досмотр по неделям'!P80)</f>
-        <v>0.00637629469886264</v>
+        <v>0.00748042792146575</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="33" t="n">
         <f aca="false">IF(K2=0,"",DATE(YEAR(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),1))</f>
-        <v>46235</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4856,38 +5748,38 @@
       </c>
       <c r="B4" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D81="",NA(),'Досмотр по неделям'!D81)</f>
-        <v>102495</v>
+        <v>108106</v>
       </c>
       <c r="C4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K81="",'Досмотр по неделям'!K81=0),NA(),'Досмотр по неделям'!K81)</f>
-        <v>4.87828674569491E-005</v>
+        <v>5.55010822711043E-005</v>
       </c>
       <c r="D4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L81="",'Досмотр по неделям'!L81=0),NA(),'Досмотр по неделям'!L81)</f>
-        <v>0.0027806234450461</v>
+        <v>0.00407932954692617</v>
       </c>
       <c r="E4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M81="",'Досмотр по неделям'!M81=0),NA(),'Досмотр по неделям'!M81)</f>
-        <v>0.00196107127176935</v>
+        <v>0.00165578228775461</v>
       </c>
       <c r="F4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N81="",'Досмотр по неделям'!N81=0),NA(),'Досмотр по неделям'!N81)</f>
-        <v>0.00122932825991512</v>
+        <v>0.00107302092390802</v>
       </c>
       <c r="G4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O81="",'Досмотр по неделям'!O81=0),NA(),'Досмотр по неделям'!O81)</f>
-        <v>9.75657349138982E-006</v>
+        <v>9.25018037851738E-006</v>
       </c>
       <c r="H4" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P81="",'Досмотр по неделям'!P81=0),NA(),'Досмотр по неделям'!P81)</f>
-        <v>0.00602956241767891</v>
+        <v>0.00687288402123841</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4" s="33" t="n">
         <f aca="false">IF(K3="","",EDATE(K3,-1))</f>
-        <v>46204</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,38 +5789,38 @@
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D82="",NA(),'Досмотр по неделям'!D82)</f>
-        <v>96686</v>
+        <v>97150</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K82="",'Досмотр по неделям'!K82=0),NA(),'Досмотр по неделям'!K82)</f>
-        <v>5.17137951720001E-005</v>
+        <v>6.17601646937725E-005</v>
       </c>
       <c r="D5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L82="",'Досмотр по неделям'!L82=0),NA(),'Досмотр по неделям'!L82)</f>
-        <v>0.00372339325238401</v>
+        <v>0.00374678332475553</v>
       </c>
       <c r="E5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M82="",'Досмотр по неделям'!M82=0),NA(),'Досмотр по неделям'!M82)</f>
-        <v>0.0016755269635728</v>
+        <v>0.00186309830159547</v>
       </c>
       <c r="F5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N82="",'Досмотр по неделям'!N82=0),NA(),'Досмотр по неделям'!N82)</f>
-        <v>0.001499700059988</v>
+        <v>0.00101904271744725</v>
       </c>
       <c r="G5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O82="",'Досмотр по неделям'!O82=0),NA(),'Досмотр по неделям'!O82)</f>
-        <v>1.03427590344E-005</v>
+        <v>1.02933607822954E-005</v>
       </c>
       <c r="H5" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P82="",'Досмотр по неделям'!P82=0),NA(),'Досмотр по неделям'!P82)</f>
-        <v>0.00696067683015121</v>
+        <v>0.00670097786927432</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K5" s="33" t="n">
         <f aca="false">IF(K3="","",EDATE(K3,1))</f>
-        <v>46266</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4938,38 +5830,38 @@
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D83="",NA(),'Досмотр по неделям'!D83)</f>
-        <v>98975</v>
+        <v>98051</v>
       </c>
       <c r="C6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K83="",'Досмотр по неделям'!K83=0),NA(),'Досмотр по неделям'!K83)</f>
-        <v>6.0621369032584E-005</v>
+        <v>5.09938705367615E-005</v>
       </c>
       <c r="D6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L83="",'Досмотр по неделям'!L83=0),NA(),'Досмотр по неделям'!L83)</f>
-        <v>0.00400101035615054</v>
+        <v>0.0035491733893586</v>
       </c>
       <c r="E6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M83="",'Досмотр по неделям'!M83=0),NA(),'Досмотр по неделям'!M83)</f>
-        <v>0.00235412983076535</v>
+        <v>0.00181538179110871</v>
       </c>
       <c r="F6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N83="",'Досмотр по неделям'!N83=0),NA(),'Досмотр по неделям'!N83)</f>
-        <v>0.00137408436473857</v>
+        <v>0.00155021366431755</v>
       </c>
       <c r="G6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O83="",'Досмотр по неделям'!O83=0),NA(),'Досмотр по неделям'!O83)</f>
-        <v>1.01035615054307E-005</v>
+        <v>1.01987741073523E-005</v>
       </c>
       <c r="H6" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P83="",'Досмотр по неделям'!P83=0),NA(),'Досмотр по неделям'!P83)</f>
-        <v>0.00779994948219247</v>
+        <v>0.00697596148942897</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="32" t="n">
         <f aca="false">IF(K3="","",COUNTIF('Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;K3)+1)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4979,38 +5871,38 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D84="",NA(),'Досмотр по неделям'!D84)</f>
-        <v>101080</v>
+        <v>105018</v>
       </c>
       <c r="C7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K84="",'Досмотр по неделям'!K84=0),NA(),'Досмотр по неделям'!K84)</f>
-        <v>3.95726157499011E-005</v>
+        <v>5.71330629035023E-005</v>
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L84="",'Досмотр по неделям'!L84=0),NA(),'Досмотр по неделям'!L84)</f>
-        <v>0.00455085081123862</v>
+        <v>0.00331371764840313</v>
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M84="",'Досмотр по неделям'!M84=0),NA(),'Досмотр по неделям'!M84)</f>
-        <v>0.00155322516818362</v>
+        <v>0.00188539107581557</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N84="",'Досмотр по неделям'!N84=0),NA(),'Досмотр по неделям'!N84)</f>
-        <v>0.00118717847249703</v>
+        <v>0.00150450398979223</v>
       </c>
       <c r="G7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O84="",'Досмотр по неделям'!O84=0),NA(),'Досмотр по неделям'!O84)</f>
-        <v>1.97863078749505E-005</v>
+        <v>1.90443543011674E-005</v>
       </c>
       <c r="H7" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P84="",'Досмотр по неделям'!P84=0),NA(),'Досмотр по неделям'!P84)</f>
-        <v>0.00735061337554412</v>
+        <v>0.0067797901312156</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K7" s="32" t="n">
         <f aca="false">IF(K6="","",IF(K6+0&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+0)&lt;K5,K6+0,"")))</f>
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5020,38 +5912,38 @@
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D85="",NA(),'Досмотр по неделям'!D85)</f>
-        <v>107342</v>
+        <v>100955</v>
       </c>
       <c r="C8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K85="",'Досмотр по неделям'!K85=0),NA(),'Досмотр по неделям'!K85)</f>
-        <v>7.4528143690261E-005</v>
+        <v>5.94324203853202E-005</v>
       </c>
       <c r="D8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L85="",'Досмотр по неделям'!L85=0),NA(),'Досмотр по неделям'!L85)</f>
-        <v>0.00400588772335153</v>
+        <v>0.00410083700658709</v>
       </c>
       <c r="E8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M85="",'Досмотр по неделям'!M85=0),NA(),'Досмотр по неделям'!M85)</f>
-        <v>0.00163030314322446</v>
+        <v>0.00166410777078897</v>
       </c>
       <c r="F8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N85="",'Досмотр по неделям'!N85=0),NA(),'Досмотр по неделям'!N85)</f>
-        <v>0.000996813921857241</v>
+        <v>0.00142637808924768</v>
       </c>
       <c r="G8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O85="",'Досмотр по неделям'!O85=0),NA(),'Досмотр по неделям'!O85)</f>
-        <v>2.79480538838479E-005</v>
+        <v>9.90540339755337E-006</v>
       </c>
       <c r="H8" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P85="",'Досмотр по неделям'!P85=0),NA(),'Досмотр по неделям'!P85)</f>
-        <v>0.00673548098600734</v>
+        <v>0.00726066069040662</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="32" t="n">
         <f aca="false">IF(K6="","",IF(K6+1&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+1)&lt;K5,K6+1,"")))</f>
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5061,38 +5953,38 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D86="",NA(),'Досмотр по неделям'!D86)</f>
-        <v>118920</v>
+        <v>107393</v>
       </c>
       <c r="C9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K86="",'Досмотр по неделям'!K86=0),NA(),'Досмотр по неделям'!K86)</f>
-        <v>5.88631012445341E-005</v>
+        <v>6.51811570586537E-005</v>
       </c>
       <c r="D9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L86="",'Досмотр по неделям'!L86=0),NA(),'Досмотр по неделям'!L86)</f>
-        <v>0.00402791792801884</v>
+        <v>0.00383637667259505</v>
       </c>
       <c r="E9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M86="",'Досмотр по неделям'!M86=0),NA(),'Досмотр по неделям'!M86)</f>
-        <v>0.0010427177934746</v>
+        <v>0.00162021733260082</v>
       </c>
       <c r="F9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N86="",'Досмотр по неделям'!N86=0),NA(),'Досмотр по неделям'!N86)</f>
-        <v>0.000992263706693576</v>
+        <v>0.000959094168148762</v>
       </c>
       <c r="G9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O86="",'Досмотр по неделям'!O86=0),NA(),'Досмотр по неделям'!O86)</f>
-        <v>8.40901446350488E-006</v>
+        <v>9.31159386552196E-006</v>
       </c>
       <c r="H9" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P86="",'Досмотр по неделям'!P86=0),NA(),'Досмотр по неделям'!P86)</f>
-        <v>0.00613017154389506</v>
+        <v>0.00649018092426881</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="32" t="n">
         <f aca="false">IF(K6="","",IF(K6+2&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+2)&lt;K5,K6+2,"")))</f>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5102,38 +5994,38 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D87="",NA(),'Досмотр по неделям'!D87)</f>
-        <v>112911</v>
+        <v>116898</v>
       </c>
       <c r="C10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K87="",'Досмотр по неделям'!K87=0),NA(),'Досмотр по неделям'!K87)</f>
-        <v>7.0852264172667E-005</v>
+        <v>5.13267977210902E-005</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L87="",'Досмотр по неделям'!L87=0),NA(),'Досмотр по неделям'!L87)</f>
-        <v>0.0033566260151801</v>
+        <v>0.00334479631815771</v>
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M87="",'Досмотр по неделям'!M87=0),NA(),'Досмотр по неделям'!M87)</f>
-        <v>0.00106278396259</v>
+        <v>0.0013259422744615</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N87="",'Досмотр по неделям'!N87=0),NA(),'Досмотр по неделям'!N87)</f>
-        <v>0.00146132794856126</v>
+        <v>0.000684357302947869</v>
       </c>
       <c r="G10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O87="",'Досмотр по неделям'!O87=0),NA(),'Досмотр по неделям'!O87)</f>
-        <v>1.77130660431667E-005</v>
+        <v>8.55446628684836E-006</v>
       </c>
       <c r="H10" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P87="",'Досмотр по неделям'!P87=0),NA(),'Досмотр по неделям'!P87)</f>
-        <v>0.00596930325654719</v>
+        <v>0.00541497715957501</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="32" t="n">
         <f aca="false">IF(K6="","",IF(K6+3&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+3)&lt;K5,K6+3,"")))</f>
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5141,40 +6033,40 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B88),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B88),"00")</f>
         <v>31.08</v>
       </c>
-      <c r="B11" s="10" t="e">
+      <c r="B11" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D88="",NA(),'Досмотр по неделям'!D88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C11" s="24" t="e">
+        <v>109740</v>
+      </c>
+      <c r="C11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K88="",'Досмотр по неделям'!K88=0),NA(),'Досмотр по неделям'!K88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D11" s="24" t="e">
+        <v>5.46746856205577E-005</v>
+      </c>
+      <c r="D11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L88="",'Досмотр по неделям'!L88=0),NA(),'Досмотр по неделям'!L88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E11" s="24" t="e">
+        <v>0.00328959358483689</v>
+      </c>
+      <c r="E11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M88="",'Досмотр по неделям'!M88=0),NA(),'Досмотр по неделям'!M88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F11" s="24" t="e">
+        <v>0.00132130490249681</v>
+      </c>
+      <c r="F11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N88="",'Досмотр по неделям'!N88=0),NA(),'Досмотр по неделям'!N88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G11" s="24" t="e">
+        <v>0.000938582103152907</v>
+      </c>
+      <c r="G11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O88="",'Досмотр по неделям'!O88=0),NA(),'Досмотр по неделям'!O88)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="24" t="e">
+        <v>1.82248952068526E-005</v>
+      </c>
+      <c r="H11" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P88="",'Досмотр по неделям'!P88=0),NA(),'Досмотр по неделям'!P88)</f>
-        <v>#N/A</v>
+        <v>0.00562238017131402</v>
       </c>
       <c r="J11" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="K11" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+4&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+4)&lt;K5,K6+4,"")))</f>
-        <v>9</v>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5182,33 +6074,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B89),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B89),"00")</f>
         <v>07.09</v>
       </c>
-      <c r="B12" s="10" t="e">
+      <c r="B12" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D89="",NA(),'Досмотр по неделям'!D89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C12" s="24" t="e">
+        <v>106757</v>
+      </c>
+      <c r="C12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K89="",'Досмотр по неделям'!K89=0),NA(),'Досмотр по неделям'!K89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D12" s="24" t="e">
+        <v>5.62024035894602E-005</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L89="",'Досмотр по неделям'!L89=0),NA(),'Досмотр по неделям'!L89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E12" s="24" t="e">
+        <v>0.00374682690596401</v>
+      </c>
+      <c r="E12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M89="",'Досмотр по неделям'!M89=0),NA(),'Досмотр по неделям'!M89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F12" s="24" t="e">
+        <v>0.00165797090588908</v>
+      </c>
+      <c r="F12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N89="",'Досмотр по неделям'!N89=0),NA(),'Досмотр по неделям'!N89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G12" s="24" t="e">
+        <v>0.00136759182067686</v>
+      </c>
+      <c r="G12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O89="",'Досмотр по неделям'!O89=0),NA(),'Досмотр по неделям'!O89)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H12" s="24" t="e">
+        <v>9.36706726491003E-006</v>
+      </c>
+      <c r="H12" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P89="",'Досмотр по неделям'!P89=0),NA(),'Досмотр по неделям'!P89)</f>
-        <v>#N/A</v>
+        <v>0.00683795910338432</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5216,33 +6108,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B90),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B90),"00")</f>
         <v>14.09</v>
       </c>
-      <c r="B13" s="10" t="e">
+      <c r="B13" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D90="",NA(),'Досмотр по неделям'!D90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="24" t="e">
+        <v>101131</v>
+      </c>
+      <c r="C13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K90="",'Досмотр по неделям'!K90=0),NA(),'Досмотр по неделям'!K90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D13" s="24" t="e">
+        <v>4.94408242774224E-005</v>
+      </c>
+      <c r="D13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L90="",'Досмотр по неделям'!L90=0),NA(),'Досмотр по неделям'!L90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E13" s="24" t="e">
+        <v>0.00354985118311893</v>
+      </c>
+      <c r="E13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M90="",'Досмотр по неделям'!M90=0),NA(),'Досмотр по неделям'!M90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F13" s="24" t="e">
+        <v>0.00165132353086591</v>
+      </c>
+      <c r="F13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N90="",'Досмотр по неделям'!N90=0),NA(),'Досмотр по неделям'!N90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="24" t="e">
+        <v>0.00131512592577943</v>
+      </c>
+      <c r="G13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O90="",'Досмотр по неделям'!O90=0),NA(),'Досмотр по неделям'!O90)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H13" s="24" t="e">
+        <v>9.88816485548447E-006</v>
+      </c>
+      <c r="H13" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P90="",'Досмотр по неделям'!P90=0),NA(),'Досмотр по неделям'!P90)</f>
-        <v>#N/A</v>
+        <v>0.00657562962889717</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5250,33 +6142,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B91),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B91),"00")</f>
         <v>21.09</v>
       </c>
-      <c r="B14" s="10" t="e">
+      <c r="B14" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D91="",NA(),'Досмотр по неделям'!D91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C14" s="24" t="e">
+        <v>103931</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K91="",'Досмотр по неделям'!K91=0),NA(),'Досмотр по неделям'!K91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D14" s="24" t="e">
+        <v>4.81088414428804E-005</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L91="",'Досмотр по неделям'!L91=0),NA(),'Досмотр по неделям'!L91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E14" s="24" t="e">
+        <v>0.00351194542533027</v>
+      </c>
+      <c r="E14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M91="",'Досмотр по неделям'!M91=0),NA(),'Досмотр по неделям'!M91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F14" s="24" t="e">
+        <v>0.00194359719429237</v>
+      </c>
+      <c r="F14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N91="",'Досмотр по неделям'!N91=0),NA(),'Досмотр по неделям'!N91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G14" s="24" t="e">
+        <v>0.00150099585301787</v>
+      </c>
+      <c r="G14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O91="",'Досмотр по неделям'!O91=0),NA(),'Досмотр по неделям'!O91)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H14" s="24" t="e">
+        <v>9.62176828857607E-006</v>
+      </c>
+      <c r="H14" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P91="",'Досмотр по неделям'!P91=0),NA(),'Досмотр по неделям'!P91)</f>
-        <v>#N/A</v>
+        <v>0.00701426908237196</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5284,33 +6176,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B92),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B92),"00")</f>
         <v>28.09</v>
       </c>
-      <c r="B15" s="10" t="e">
+      <c r="B15" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D92="",NA(),'Досмотр по неделям'!D92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C15" s="24" t="e">
+        <v>96072</v>
+      </c>
+      <c r="C15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K92="",'Досмотр по неделям'!K92=0),NA(),'Досмотр по неделям'!K92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D15" s="24" t="e">
+        <v>5.20443001082521E-005</v>
+      </c>
+      <c r="D15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L92="",'Досмотр по неделям'!L92=0),NA(),'Досмотр по неделям'!L92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E15" s="24" t="e">
+        <v>0.00473603130985095</v>
+      </c>
+      <c r="E15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M92="",'Досмотр по неделям'!M92=0),NA(),'Досмотр по неделям'!M92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F15" s="24" t="e">
+        <v>0.00167582646348572</v>
+      </c>
+      <c r="F15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N92="",'Досмотр по неделям'!N92=0),NA(),'Досмотр по неделям'!N92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G15" s="24" t="e">
+        <v>0.00100965942210009</v>
+      </c>
+      <c r="G15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O92="",'Досмотр по неделям'!O92=0),NA(),'Досмотр по неделям'!O92)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H15" s="24" t="e">
+        <v>1.04088600216504E-005</v>
+      </c>
+      <c r="H15" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P92="",'Досмотр по неделям'!P92=0),NA(),'Досмотр по неделям'!P92)</f>
-        <v>#N/A</v>
+        <v>0.00748397035556666</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5318,33 +6210,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B93),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B93),"00")</f>
         <v>05.10</v>
       </c>
-      <c r="B16" s="10" t="e">
+      <c r="B16" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D93="",NA(),'Досмотр по неделям'!D93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C16" s="24" t="e">
+        <v>113958</v>
+      </c>
+      <c r="C16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K93="",'Досмотр по неделям'!K93=0),NA(),'Досмотр по неделям'!K93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D16" s="24" t="e">
+        <v>6.14261394548869E-005</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L93="",'Досмотр по неделям'!L93=0),NA(),'Досмотр по неделям'!L93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E16" s="24" t="e">
+        <v>0.00352761543726636</v>
+      </c>
+      <c r="E16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M93="",'Досмотр по неделям'!M93=0),NA(),'Досмотр по неделям'!M93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F16" s="24" t="e">
+        <v>0.00142157637024167</v>
+      </c>
+      <c r="F16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N93="",'Досмотр по неделям'!N93=0),NA(),'Досмотр по неделям'!N93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G16" s="24" t="e">
+        <v>0.00119342213798066</v>
+      </c>
+      <c r="G16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O93="",'Досмотр по неделям'!O93=0),NA(),'Досмотр по неделям'!O93)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H16" s="24" t="e">
+        <v>8.77516277926956E-006</v>
+      </c>
+      <c r="H16" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P93="",'Досмотр по неделям'!P93=0),NA(),'Досмотр по неделям'!P93)</f>
-        <v>#N/A</v>
+        <v>0.00621281524772285</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,33 +6244,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B94),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B94),"00")</f>
         <v>12.10</v>
       </c>
-      <c r="B17" s="10" t="e">
+      <c r="B17" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D94="",NA(),'Досмотр по неделям'!D94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C17" s="24" t="e">
+        <v>111533</v>
+      </c>
+      <c r="C17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K94="",'Досмотр по неделям'!K94=0),NA(),'Досмотр по неделям'!K94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D17" s="24" t="e">
+        <v>6.27616938484574E-005</v>
+      </c>
+      <c r="D17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L94="",'Досмотр по неделям'!L94=0),NA(),'Досмотр по неделям'!L94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E17" s="24" t="e">
+        <v>0.00238494436624138</v>
+      </c>
+      <c r="E17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M94="",'Досмотр по неделям'!M94=0),NA(),'Досмотр по неделям'!M94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F17" s="24" t="e">
+        <v>0.00156904234621144</v>
+      </c>
+      <c r="F17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N94="",'Досмотр по неделям'!N94=0),NA(),'Досмотр по неделям'!N94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G17" s="24" t="e">
+        <v>0.00126419983323321</v>
+      </c>
+      <c r="G17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O94="",'Досмотр по неделям'!O94=0),NA(),'Досмотр по неделям'!O94)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H17" s="24" t="e">
+        <v>1.79319125281307E-005</v>
+      </c>
+      <c r="H17" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P94="",'Досмотр по неделям'!P94=0),NA(),'Досмотр по неделям'!P94)</f>
-        <v>#N/A</v>
+        <v>0.00529888015206262</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5386,33 +6278,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B95),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B95),"00")</f>
         <v>19.10</v>
       </c>
-      <c r="B18" s="10" t="e">
+      <c r="B18" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D95="",NA(),'Досмотр по неделям'!D95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C18" s="24" t="e">
+        <v>95764</v>
+      </c>
+      <c r="C18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K95="",'Досмотр по неделям'!K95=0),NA(),'Досмотр по неделям'!K95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D18" s="24" t="e">
+        <v>5.22116870640324E-005</v>
+      </c>
+      <c r="D18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L95="",'Досмотр по неделям'!L95=0),NA(),'Досмотр по неделям'!L95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E18" s="24" t="e">
+        <v>0.00388454951756401</v>
+      </c>
+      <c r="E18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M95="",'Досмотр по неделям'!M95=0),NA(),'Досмотр по неделям'!M95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F18" s="24" t="e">
+        <v>0.00137838853849046</v>
+      </c>
+      <c r="F18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N95="",'Досмотр по неделям'!N95=0),NA(),'Досмотр по неделям'!N95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G18" s="24" t="e">
+        <v>0.00147236957520571</v>
+      </c>
+      <c r="G18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O95="",'Досмотр по неделям'!O95=0),NA(),'Досмотр по неделям'!O95)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H18" s="24" t="e">
+        <v>2.0884674825613E-005</v>
+      </c>
+      <c r="H18" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P95="",'Досмотр по неделям'!P95=0),NA(),'Досмотр по неделям'!P95)</f>
-        <v>#N/A</v>
+        <v>0.00680840399314983</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,33 +6312,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B96),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B96),"00")</f>
         <v>26.10</v>
       </c>
-      <c r="B19" s="10" t="e">
+      <c r="B19" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D96="",NA(),'Досмотр по неделям'!D96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C19" s="24" t="e">
+        <v>93118</v>
+      </c>
+      <c r="C19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K96="",'Досмотр по неделям'!K96=0),NA(),'Досмотр по неделям'!K96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D19" s="24" t="e">
+        <v>6.44343735904981E-005</v>
+      </c>
+      <c r="D19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L96="",'Досмотр по неделям'!L96=0),NA(),'Досмотр по неделям'!L96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E19" s="24" t="e">
+        <v>0.0043600592796237</v>
+      </c>
+      <c r="E19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M96="",'Досмотр по неделям'!M96=0),NA(),'Досмотр по неделям'!M96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F19" s="24" t="e">
+        <v>0.00204042183036577</v>
+      </c>
+      <c r="F19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N96="",'Досмотр по неделям'!N96=0),NA(),'Досмотр по неделям'!N96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G19" s="24" t="e">
+        <v>0.0016430765265577</v>
+      </c>
+      <c r="G19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O96="",'Досмотр по неделям'!O96=0),NA(),'Досмотр по неделям'!O96)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H19" s="24" t="e">
+        <v>2.1478124530166E-005</v>
+      </c>
+      <c r="H19" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P96="",'Досмотр по неделям'!P96=0),NA(),'Досмотр по неделям'!P96)</f>
-        <v>#N/A</v>
+        <v>0.00812947013466784</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5454,33 +6346,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B97),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B97),"00")</f>
         <v>02.11</v>
       </c>
-      <c r="B20" s="10" t="e">
+      <c r="B20" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D97="",NA(),'Досмотр по неделям'!D97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C20" s="24" t="e">
+        <v>99072</v>
+      </c>
+      <c r="C20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K97="",'Досмотр по неделям'!K97=0),NA(),'Досмотр по неделям'!K97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D20" s="24" t="e">
+        <v>7.0655684754522E-005</v>
+      </c>
+      <c r="D20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L97="",'Досмотр по неделям'!L97=0),NA(),'Досмотр по неделям'!L97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E20" s="24" t="e">
+        <v>0.00405765503875969</v>
+      </c>
+      <c r="E20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M97="",'Досмотр по неделям'!M97=0),NA(),'Досмотр по неделям'!M97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F20" s="24" t="e">
+        <v>0.00189760981912145</v>
+      </c>
+      <c r="F20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N97="",'Досмотр по неделям'!N97=0),NA(),'Досмотр по неделям'!N97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G20" s="24" t="e">
+        <v>0.00150395671834625</v>
+      </c>
+      <c r="G20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O97="",'Досмотр по неделям'!O97=0),NA(),'Досмотр по неделям'!O97)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H20" s="24" t="e">
+        <v>1.0093669250646E-005</v>
+      </c>
+      <c r="H20" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P97="",'Досмотр по неделям'!P97=0),NA(),'Досмотр по неделям'!P97)</f>
-        <v>#N/A</v>
+        <v>0.00753997093023256</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5488,33 +6380,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B98),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B98),"00")</f>
         <v>09.11</v>
       </c>
-      <c r="B21" s="10" t="e">
+      <c r="B21" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D98="",NA(),'Досмотр по неделям'!D98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C21" s="24" t="e">
+        <v>100312</v>
+      </c>
+      <c r="C21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K98="",'Досмотр по неделям'!K98=0),NA(),'Досмотр по неделям'!K98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D21" s="24" t="e">
+        <v>7.97511763298509E-005</v>
+      </c>
+      <c r="D21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L98="",'Досмотр по неделям'!L98=0),NA(),'Досмотр по неделям'!L98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E21" s="24" t="e">
+        <v>0.00504426190286307</v>
+      </c>
+      <c r="E21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M98="",'Досмотр по неделям'!M98=0),NA(),'Досмотр по неделям'!M98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F21" s="24" t="e">
+        <v>0.00166480580588564</v>
+      </c>
+      <c r="F21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N98="",'Досмотр по неделям'!N98=0),NA(),'Досмотр по неделям'!N98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G21" s="24" t="e">
+        <v>0.000927107424834516</v>
+      </c>
+      <c r="G21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O98="",'Досмотр по неделям'!O98=0),NA(),'Досмотр по неделям'!O98)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H21" s="24" t="e">
+        <v>9.96889704123136E-006</v>
+      </c>
+      <c r="H21" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P98="",'Досмотр по неделям'!P98=0),NA(),'Досмотр по неделям'!P98)</f>
-        <v>#N/A</v>
+        <v>0.0077258952069543</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5522,33 +6414,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B99),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B99),"00")</f>
         <v>16.11</v>
       </c>
-      <c r="B22" s="10" t="e">
+      <c r="B22" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D99="",NA(),'Досмотр по неделям'!D99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C22" s="24" t="e">
+        <v>108756</v>
+      </c>
+      <c r="C22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K99="",'Досмотр по неделям'!K99=0),NA(),'Досмотр по неделям'!K99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D22" s="24" t="e">
+        <v>6.43642649600942E-005</v>
+      </c>
+      <c r="D22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L99="",'Досмотр по неделям'!L99=0),NA(),'Досмотр по неделям'!L99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E22" s="24" t="e">
+        <v>0.00419287211740042</v>
+      </c>
+      <c r="E22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M99="",'Досмотр по неделям'!M99=0),NA(),'Досмотр по неделям'!M99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F22" s="24" t="e">
+        <v>0.00120453124425319</v>
+      </c>
+      <c r="F22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N99="",'Досмотр по неделям'!N99=0),NA(),'Досмотр по неделям'!N99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G22" s="24" t="e">
+        <v>0.00120453124425319</v>
+      </c>
+      <c r="G22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O99="",'Досмотр по неделям'!O99=0),NA(),'Досмотр по неделям'!O99)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H22" s="24" t="e">
+        <v>9.19489499429917E-006</v>
+      </c>
+      <c r="H22" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P99="",'Досмотр по неделям'!P99=0),NA(),'Досмотр по неделям'!P99)</f>
-        <v>#N/A</v>
+        <v>0.00667549376586119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5556,33 +6448,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B100),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B100),"00")</f>
         <v>23.11</v>
       </c>
-      <c r="B23" s="10" t="e">
+      <c r="B23" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D100="",NA(),'Досмотр по неделям'!D100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C23" s="24" t="e">
+        <v>106103</v>
+      </c>
+      <c r="C23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K100="",'Досмотр по неделям'!K100=0),NA(),'Досмотр по неделям'!K100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D23" s="24" t="e">
+        <v>6.59736293978493E-005</v>
+      </c>
+      <c r="D23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L100="",'Досмотр по неделям'!L100=0),NA(),'Досмотр по неделям'!L100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E23" s="24" t="e">
+        <v>0.00368509844207987</v>
+      </c>
+      <c r="E23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M100="",'Досмотр по неделям'!M100=0),NA(),'Досмотр по неделям'!M100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F23" s="24" t="e">
+        <v>0.00157394230134869</v>
+      </c>
+      <c r="F23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N100="",'Досмотр по неделям'!N100=0),NA(),'Досмотр по неделям'!N100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G23" s="24" t="e">
+        <v>0.00123464935015975</v>
+      </c>
+      <c r="G23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O100="",'Досмотр по неделям'!O100=0),NA(),'Досмотр по неделям'!O100)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H23" s="24" t="e">
+        <v>1.88496083993855E-005</v>
+      </c>
+      <c r="H23" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P100="",'Досмотр по неделям'!P100=0),NA(),'Досмотр по неделям'!P100)</f>
-        <v>#N/A</v>
+        <v>0.00657851333138554</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5590,33 +6482,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B101),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B101),"00")</f>
         <v>30.11</v>
       </c>
-      <c r="B24" s="10" t="e">
+      <c r="B24" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D101="",NA(),'Досмотр по неделям'!D101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C24" s="24" t="e">
+        <v>104608</v>
+      </c>
+      <c r="C24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K101="",'Досмотр по неделям'!K101=0),NA(),'Досмотр по неделям'!K101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D24" s="24" t="e">
+        <v>5.73569899051698E-005</v>
+      </c>
+      <c r="D24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L101="",'Досмотр по неделям'!L101=0),NA(),'Досмотр по неделям'!L101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E24" s="24" t="e">
+        <v>0.0031068369531967</v>
+      </c>
+      <c r="E24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M101="",'Досмотр по неделям'!M101=0),NA(),'Досмотр по неделям'!M101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F24" s="24" t="e">
+        <v>0.00167291220556745</v>
+      </c>
+      <c r="F24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N101="",'Досмотр по неделям'!N101=0),NA(),'Досмотр по неделям'!N101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G24" s="24" t="e">
+        <v>0.00146260324258183</v>
+      </c>
+      <c r="G24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O101="",'Досмотр по неделям'!O101=0),NA(),'Досмотр по неделям'!O101)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H24" s="24" t="e">
+        <v>1.91189966350566E-005</v>
+      </c>
+      <c r="H24" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P101="",'Досмотр по неделям'!P101=0),NA(),'Досмотр по неделям'!P101)</f>
-        <v>#N/A</v>
+        <v>0.0063188283878862</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5624,33 +6516,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B102),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B102),"00")</f>
         <v>07.12</v>
       </c>
-      <c r="B25" s="10" t="e">
+      <c r="B25" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D102="",NA(),'Досмотр по неделям'!D102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="24" t="e">
+        <v>101748</v>
+      </c>
+      <c r="C25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K102="",'Досмотр по неделям'!K102=0),NA(),'Досмотр по неделям'!K102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="24" t="e">
+        <v>5.89692180681684E-005</v>
+      </c>
+      <c r="D25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L102="",'Досмотр по неделям'!L102=0),NA(),'Досмотр по неделям'!L102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="24" t="e">
+        <v>0.00464874002437394</v>
+      </c>
+      <c r="E25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M102="",'Досмотр по неделям'!M102=0),NA(),'Досмотр по неделям'!M102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="24" t="e">
+        <v>0.00196564060227228</v>
+      </c>
+      <c r="F25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N102="",'Досмотр по неделям'!N102=0),NA(),'Досмотр по неделям'!N102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="24" t="e">
+        <v>0.00138577662460196</v>
+      </c>
+      <c r="G25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O102="",'Досмотр по неделям'!O102=0),NA(),'Досмотр по неделям'!O102)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="24" t="e">
+        <v>9.8282030113614E-006</v>
+      </c>
+      <c r="H25" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P102="",'Досмотр по неделям'!P102=0),NA(),'Досмотр по неделям'!P102)</f>
-        <v>#N/A</v>
+        <v>0.00806895467232771</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,33 +6550,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B103),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B103),"00")</f>
         <v>14.12</v>
       </c>
-      <c r="B26" s="10" t="e">
+      <c r="B26" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D103="",NA(),'Досмотр по неделям'!D103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C26" s="24" t="e">
+        <v>98516</v>
+      </c>
+      <c r="C26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K103="",'Досмотр по неделям'!K103=0),NA(),'Досмотр по неделям'!K103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D26" s="24" t="e">
+        <v>7.10544480084453E-005</v>
+      </c>
+      <c r="D26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L103="",'Досмотр по неделям'!L103=0),NA(),'Досмотр по неделям'!L103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E26" s="24" t="e">
+        <v>0.00423281497421739</v>
+      </c>
+      <c r="E26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M103="",'Досмотр по неделям'!M103=0),NA(),'Досмотр по неделям'!M103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F26" s="24" t="e">
+        <v>0.00208088026310447</v>
+      </c>
+      <c r="F26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N103="",'Досмотр по неделям'!N103=0),NA(),'Досмотр по неделям'!N103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G26" s="24" t="e">
+        <v>0.00164440293962402</v>
+      </c>
+      <c r="G26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O103="",'Досмотр по неделям'!O103=0),NA(),'Досмотр по неделям'!O103)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H26" s="24" t="e">
+        <v>1.01506354297779E-005</v>
+      </c>
+      <c r="H26" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P103="",'Досмотр по неделям'!P103=0),NA(),'Досмотр по неделям'!P103)</f>
-        <v>#N/A</v>
+        <v>0.0080393032603841</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5692,33 +6584,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B104),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B104),"00")</f>
         <v>21.12</v>
       </c>
-      <c r="B27" s="10" t="e">
+      <c r="B27" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D104="",NA(),'Досмотр по неделям'!D104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C27" s="24" t="e">
+        <v>99299</v>
+      </c>
+      <c r="C27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K104="",'Досмотр по неделям'!K104=0),NA(),'Досмотр по неделям'!K104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D27" s="24" t="e">
+        <v>7.04941640902728E-005</v>
+      </c>
+      <c r="D27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L104="",'Досмотр по неделям'!L104=0),NA(),'Досмотр по неделям'!L104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="24" t="e">
+        <v>0.00459219126073777</v>
+      </c>
+      <c r="E27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M104="",'Досмотр по неделям'!M104=0),NA(),'Досмотр по неделям'!M104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F27" s="24" t="e">
+        <v>0.00183284826634709</v>
+      </c>
+      <c r="F27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N104="",'Досмотр по неделям'!N104=0),NA(),'Досмотр по неделям'!N104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G27" s="24" t="e">
+        <v>0.00108762424596421</v>
+      </c>
+      <c r="G27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O104="",'Досмотр по неделям'!O104=0),NA(),'Досмотр по неделям'!O104)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H27" s="24" t="e">
+        <v>1.0070594870039E-005</v>
+      </c>
+      <c r="H27" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P104="",'Досмотр по неделям'!P104=0),NA(),'Досмотр по неделям'!P104)</f>
-        <v>#N/A</v>
+        <v>0.00759322853200939</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5726,33 +6618,33 @@
         <f aca="false">TEXT(DAY('Досмотр по неделям'!B105),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B105),"00")</f>
         <v>28.12</v>
       </c>
-      <c r="B28" s="10" t="e">
+      <c r="B28" s="10" t="n">
         <f aca="false">IF('Досмотр по неделям'!D105="",NA(),'Досмотр по неделям'!D105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C28" s="24" t="e">
+        <v>110550</v>
+      </c>
+      <c r="C28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!K105="",'Досмотр по неделям'!K105=0),NA(),'Досмотр по неделям'!K105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D28" s="24" t="e">
+        <v>6.33197648123021E-005</v>
+      </c>
+      <c r="D28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!L105="",'Досмотр по неделям'!L105=0),NA(),'Досмотр по неделям'!L105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E28" s="24" t="e">
+        <v>0.00454997738579828</v>
+      </c>
+      <c r="E28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!M105="",'Досмотр по неделям'!M105=0),NA(),'Досмотр по неделям'!M105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F28" s="24" t="e">
+        <v>0.00144730890999548</v>
+      </c>
+      <c r="F28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!N105="",'Досмотр по неделям'!N105=0),NA(),'Досмотр по неделям'!N105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G28" s="24" t="e">
+        <v>0.000931705110809588</v>
+      </c>
+      <c r="G28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!O105="",'Досмотр по неделям'!O105=0),NA(),'Досмотр по неделям'!O105)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H28" s="24" t="e">
+        <v>9.04568068747173E-006</v>
+      </c>
+      <c r="H28" s="24" t="n">
         <f aca="false">IF(OR('Досмотр по неделям'!P105="",'Досмотр по неделям'!P105=0),NA(),'Досмотр по неделям'!P105)</f>
-        <v>#N/A</v>
+        <v>0.00700135685210312</v>
       </c>
     </row>
   </sheetData>
